--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -793,10 +793,10 @@
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -889,13 +889,13 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D12" t="n">
         <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="L12" t="n">
-        <v>959</v>
+        <v>977</v>
       </c>
     </row>
     <row r="13">
@@ -929,13 +929,13 @@
         <v>5353</v>
       </c>
       <c r="C13" t="n">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="D13" t="n">
         <v>1220</v>
       </c>
       <c r="E13" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F13" t="n">
         <v>414</v>
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="L13" t="n">
-        <v>13168</v>
+        <v>13187</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D529"/>
+  <dimension ref="A1:D531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="165">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="170">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="205">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="216">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="256">
@@ -7678,21 +7678,21 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -7708,11 +7708,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -7748,11 +7748,11 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340">
@@ -7768,11 +7768,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -7828,11 +7828,11 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -7848,11 +7848,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345">
@@ -7863,16 +7863,16 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="346">
@@ -7888,11 +7888,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="347">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348">
@@ -7928,11 +7928,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
@@ -7988,11 +7988,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="352">
@@ -8008,11 +8008,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="353">
@@ -8023,16 +8023,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="354">
@@ -8048,11 +8048,11 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355">
@@ -8068,11 +8068,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -8108,11 +8108,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
@@ -8143,16 +8143,16 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="361">
@@ -8188,11 +8188,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -8208,11 +8208,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="363">
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364">
@@ -8248,11 +8248,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="365">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="366">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="368">
@@ -8323,16 +8323,16 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="370">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="371">
@@ -8388,11 +8388,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372">
@@ -8408,11 +8408,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -8428,11 +8428,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="374">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="376">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="377">
@@ -8503,16 +8503,16 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="378">
@@ -8528,11 +8528,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -8563,16 +8563,16 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -8588,11 +8588,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -8608,11 +8608,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387">
@@ -8703,16 +8703,16 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="388">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="391">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="392">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="393">
@@ -8828,11 +8828,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="396">
@@ -8888,11 +8888,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="397">
@@ -8903,16 +8903,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="398">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400">
@@ -8968,11 +8968,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="401">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -9008,11 +9008,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
@@ -9028,31 +9028,31 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="405">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D405" t="n">
@@ -9088,11 +9088,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D411" t="n">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="415">
@@ -9268,11 +9268,11 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D416" t="n">
@@ -9308,11 +9308,11 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="421">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -9428,11 +9428,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="424">
@@ -9448,11 +9448,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="425">
@@ -9468,11 +9468,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="426">
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
@@ -9503,16 +9503,16 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="428">
@@ -9528,11 +9528,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D429" t="n">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -9583,16 +9583,16 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -9628,11 +9628,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="435">
@@ -9668,11 +9668,11 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D436" t="n">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D437" t="n">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -9748,11 +9748,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="440">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="442">
@@ -9803,16 +9803,16 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -9828,11 +9828,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="444">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D444" t="n">
@@ -9868,11 +9868,11 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="447">
@@ -9908,11 +9908,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="448">
@@ -9928,11 +9928,11 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D451" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -10028,11 +10028,11 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -10048,31 +10048,31 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="457">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="458">
@@ -10128,11 +10128,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
@@ -10148,11 +10148,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="460">
@@ -10168,11 +10168,11 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="461">
@@ -10188,11 +10188,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="462">
@@ -10208,11 +10208,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="463">
@@ -10228,11 +10228,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>115</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -10243,16 +10243,16 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467">
@@ -10308,11 +10308,11 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="468">
@@ -10328,11 +10328,11 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D469" t="n">
@@ -10368,11 +10368,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="471">
@@ -10388,11 +10388,11 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472">
@@ -10403,16 +10403,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="473">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D473" t="n">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -10488,11 +10488,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D477" t="n">
@@ -10528,11 +10528,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="480">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="481">
@@ -10588,11 +10588,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="483">
@@ -10628,11 +10628,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="486">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="487">
@@ -10708,11 +10708,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="488">
@@ -10728,11 +10728,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="490">
@@ -10768,11 +10768,11 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="491">
@@ -10788,11 +10788,11 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="496">
@@ -10888,11 +10888,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="497">
@@ -10908,11 +10908,11 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="499">
@@ -10948,11 +10948,11 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D501" t="n">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D502" t="n">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -11043,12 +11043,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D504" t="n">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D505" t="n">
@@ -11088,11 +11088,11 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="507">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D507" t="n">
@@ -11128,11 +11128,11 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="510">
@@ -11168,11 +11168,11 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="511">
@@ -11183,16 +11183,16 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="512">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="513">
@@ -11228,11 +11228,11 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="514">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="518">
@@ -11328,11 +11328,11 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="519">
@@ -11343,16 +11343,16 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521">
@@ -11388,11 +11388,11 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -11408,11 +11408,11 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="523">
@@ -11423,16 +11423,16 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="524">
@@ -11443,16 +11443,16 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="525">
@@ -11468,11 +11468,11 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="526">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
@@ -11508,11 +11508,11 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -11528,11 +11528,11 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="529">
@@ -11548,10 +11548,50 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D529" t="n">
+      <c r="D531" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -489,7 +489,7 @@
         <v>3071</v>
       </c>
       <c r="C2" t="n">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D2" t="n">
         <v>361</v>
@@ -513,10 +513,10 @@
         <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L2" t="n">
-        <v>5652</v>
+        <v>5656</v>
       </c>
     </row>
     <row r="3">
@@ -566,13 +566,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C4" t="n">
         <v>205</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E4" t="n">
         <v>23</v>
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C5" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D5" t="n">
         <v>161</v>
@@ -627,16 +627,16 @@
         <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J5" t="n">
         <v>143</v>
       </c>
       <c r="K5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="6">
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C6" t="n">
         <v>239</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" t="n">
         <v>31</v>
@@ -667,16 +667,16 @@
         <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J6" t="n">
         <v>104</v>
       </c>
       <c r="K6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L6" t="n">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="7">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C7" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D7" t="n">
         <v>222</v>
@@ -698,7 +698,7 @@
         <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
@@ -713,10 +713,10 @@
         <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L7" t="n">
-        <v>1708</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="8">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" t="n">
         <v>40</v>
@@ -738,7 +738,7 @@
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -747,16 +747,16 @@
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J8" t="n">
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" t="n">
         <v>66</v>
@@ -787,16 +787,16 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L9" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -849,7 +849,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
@@ -873,7 +873,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>64</v>
@@ -889,10 +889,10 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="L12" t="n">
-        <v>977</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="13">
@@ -929,10 +929,10 @@
         <v>5353</v>
       </c>
       <c r="C13" t="n">
-        <v>2669</v>
+        <v>2673</v>
       </c>
       <c r="D13" t="n">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E13" t="n">
         <v>301</v>
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>693</v>
+        <v>742</v>
       </c>
       <c r="L13" t="n">
-        <v>13187</v>
+        <v>13241</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D531"/>
+  <dimension ref="A1:D538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1728,31 +1728,31 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -1768,11 +1768,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
@@ -1788,11 +1788,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1808,11 +1808,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
@@ -1828,11 +1828,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -1868,11 +1868,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
@@ -1888,11 +1888,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
@@ -1908,11 +1908,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48">
@@ -1923,16 +1923,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>673</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49">
@@ -1948,11 +1948,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>54</v>
+        <v>675</v>
       </c>
     </row>
     <row r="50">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>307</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51">
@@ -1988,11 +1988,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
     </row>
     <row r="52">
@@ -2008,11 +2008,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>216</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54">
@@ -2048,11 +2048,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>455</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>353</v>
+        <v>455</v>
       </c>
     </row>
     <row r="56">
@@ -2088,11 +2088,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>199</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57">
@@ -2108,11 +2108,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2974</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58">
@@ -2123,16 +2123,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>201</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="59">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -2188,11 +2188,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62">
@@ -2208,11 +2208,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -2228,11 +2228,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64">
@@ -2248,11 +2248,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
@@ -2268,11 +2268,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>123</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66">
@@ -2288,11 +2288,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>26</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67">
@@ -2308,11 +2308,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>336</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
@@ -2323,16 +2323,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>60</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69">
@@ -2348,11 +2348,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70">
@@ -2368,11 +2368,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
@@ -2408,11 +2408,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2428,11 +2428,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -2448,11 +2448,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
@@ -2468,11 +2468,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
@@ -2488,11 +2488,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77">
@@ -2508,11 +2508,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>108</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
@@ -2523,16 +2523,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>399</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79">
@@ -2548,11 +2548,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80">
@@ -2568,11 +2568,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>166</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
@@ -2588,11 +2588,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>166</v>
       </c>
     </row>
     <row r="82">
@@ -2608,11 +2608,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -2628,11 +2628,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -2648,11 +2648,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>185</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85">
@@ -2668,11 +2668,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>205</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86">
@@ -2688,11 +2688,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>76</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87">
@@ -2708,11 +2708,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>454</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88">
@@ -2723,16 +2723,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>343</v>
+        <v>451</v>
       </c>
     </row>
     <row r="89">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13</v>
+        <v>342</v>
       </c>
     </row>
     <row r="90">
@@ -2768,11 +2768,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91">
@@ -2788,11 +2788,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>7</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -2828,11 +2828,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94">
@@ -2848,11 +2848,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>137</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95">
@@ -2868,11 +2868,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>159</v>
+        <v>137</v>
       </c>
     </row>
     <row r="96">
@@ -2888,11 +2888,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>51</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97">
@@ -2908,11 +2908,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>441</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98">
@@ -2923,16 +2923,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>24</v>
+        <v>442</v>
       </c>
     </row>
     <row r="99">
@@ -2948,11 +2948,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100">
@@ -2968,11 +2968,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2988,11 +2988,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -3008,11 +3008,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -3028,11 +3028,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
@@ -3048,11 +3048,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105">
@@ -3068,11 +3068,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106">
@@ -3088,11 +3088,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3103,16 +3103,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>128</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
@@ -3128,11 +3128,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109">
@@ -3148,11 +3148,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110">
@@ -3168,11 +3168,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="111">
@@ -3188,11 +3188,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -3228,11 +3228,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114">
@@ -3248,11 +3248,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115">
@@ -3268,11 +3268,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
     </row>
     <row r="116">
@@ -3288,11 +3288,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>273</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117">
@@ -3303,16 +3303,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>230</v>
+        <v>273</v>
       </c>
     </row>
     <row r="118">
@@ -3328,11 +3328,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>12</v>
+        <v>230</v>
       </c>
     </row>
     <row r="119">
@@ -3348,11 +3348,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>92</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120">
@@ -3368,11 +3368,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="121">
@@ -3388,11 +3388,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122">
@@ -3408,11 +3408,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="123">
@@ -3428,11 +3428,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>101</v>
+        <v>29</v>
       </c>
     </row>
     <row r="124">
@@ -3448,11 +3448,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="125">
@@ -3468,11 +3468,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>48</v>
+        <v>119</v>
       </c>
     </row>
     <row r="126">
@@ -3488,11 +3488,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>307</v>
+        <v>47</v>
       </c>
     </row>
     <row r="127">
@@ -3503,16 +3503,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128">
@@ -3528,11 +3528,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
@@ -3608,11 +3608,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133">
@@ -3623,16 +3623,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134">
@@ -3648,11 +3648,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="135">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -3688,11 +3688,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137">
@@ -3708,11 +3708,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -3728,11 +3728,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139">
@@ -3748,11 +3748,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="141">
@@ -3788,11 +3788,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142">
@@ -3808,31 +3808,31 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>93</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
     </row>
     <row r="144">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -3903,16 +3903,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -3968,11 +3968,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -4048,11 +4048,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -4063,12 +4063,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -4103,16 +4103,16 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -4128,11 +4128,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -4163,16 +4163,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -4188,11 +4188,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -4228,31 +4228,31 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -4268,11 +4268,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="166">
@@ -4288,11 +4288,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167">
@@ -4308,11 +4308,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
@@ -4328,11 +4328,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>109</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="171">
@@ -4383,16 +4383,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -4408,11 +4408,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="173">
@@ -4428,11 +4428,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175">
@@ -4468,11 +4468,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -4528,11 +4528,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179">
@@ -4548,11 +4548,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180">
@@ -4568,11 +4568,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
     </row>
     <row r="181">
@@ -4583,16 +4583,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="182">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="183">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -4688,11 +4688,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188">
@@ -4728,11 +4728,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189">
@@ -4748,11 +4748,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190">
@@ -4763,16 +4763,16 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="191">
@@ -4788,11 +4788,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="192">
@@ -4808,11 +4808,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
@@ -4848,11 +4848,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195">
@@ -4868,11 +4868,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197">
@@ -4908,11 +4908,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198">
@@ -4923,16 +4923,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>154</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199">
@@ -4948,11 +4948,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>4</v>
+        <v>157</v>
       </c>
     </row>
     <row r="200">
@@ -4968,11 +4968,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201">
@@ -4988,11 +4988,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="202">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="204">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205">
@@ -5068,11 +5068,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="206">
@@ -5088,11 +5088,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
     </row>
     <row r="207">
@@ -5108,11 +5108,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>122</v>
+        <v>30</v>
       </c>
     </row>
     <row r="208">
@@ -5123,16 +5123,16 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="209">
@@ -5148,11 +5148,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="210">
@@ -5168,11 +5168,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -5188,11 +5188,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="212">
@@ -5208,11 +5208,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -5228,11 +5228,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214">
@@ -5248,11 +5248,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="215">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="216">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="217">
@@ -5308,11 +5308,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>90</v>
+        <v>13</v>
       </c>
     </row>
     <row r="218">
@@ -5323,16 +5323,16 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>10</v>
+        <v>91</v>
       </c>
     </row>
     <row r="219">
@@ -5348,11 +5348,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220">
@@ -5368,11 +5368,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -5408,11 +5408,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
@@ -5423,16 +5423,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="224">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="225">
@@ -5468,11 +5468,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -5488,11 +5488,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="227">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -5528,11 +5528,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -5548,11 +5548,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="230">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231">
@@ -5588,11 +5588,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232">
@@ -5603,16 +5603,16 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="233">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="234">
@@ -5648,11 +5648,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
@@ -5668,11 +5668,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -5708,11 +5708,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="238">
@@ -5728,11 +5728,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="240">
@@ -5768,11 +5768,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="241">
@@ -5788,11 +5788,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
     </row>
     <row r="242">
@@ -5803,16 +5803,16 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
     </row>
     <row r="243">
@@ -5828,11 +5828,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247">
@@ -5903,16 +5903,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -5928,11 +5928,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="249">
@@ -5948,11 +5948,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="250">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="252">
@@ -6008,11 +6008,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="253">
@@ -6028,11 +6028,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="254">
@@ -6048,11 +6048,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="255">
@@ -6068,31 +6068,31 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="257">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -6128,11 +6128,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -6163,16 +6163,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -6203,16 +6203,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -6228,11 +6228,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -6303,16 +6303,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="269">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -6368,11 +6368,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276">
@@ -6483,16 +6483,16 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="277">
@@ -6508,11 +6508,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -6588,11 +6588,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -6603,16 +6603,16 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283">
@@ -6628,11 +6628,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -6668,11 +6668,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
@@ -6683,16 +6683,16 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -6708,11 +6708,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -6803,16 +6803,16 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293">
@@ -6828,11 +6828,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
@@ -6848,11 +6848,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296">
@@ -6883,16 +6883,16 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="298">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -6988,31 +6988,31 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>268</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303">
@@ -7028,11 +7028,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>5</v>
+        <v>268</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="306">
@@ -7088,11 +7088,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="308">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>151</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309">
@@ -7148,11 +7148,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>46</v>
+        <v>151</v>
       </c>
     </row>
     <row r="310">
@@ -7168,11 +7168,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="311">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312">
@@ -7203,16 +7203,16 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
     </row>
     <row r="313">
@@ -7228,11 +7228,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
     </row>
     <row r="314">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="316">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D316" t="n">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="319">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -7383,16 +7383,16 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="323">
@@ -7423,16 +7423,16 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D325" t="n">
@@ -7483,16 +7483,16 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -7548,31 +7548,31 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -7623,16 +7623,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7663,16 +7663,16 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -7698,37 +7698,37 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D338" t="n">
@@ -7738,61 +7738,61 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="343">
@@ -7828,11 +7828,11 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -7848,11 +7848,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -7868,11 +7868,11 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -7883,16 +7883,16 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347">
@@ -7903,16 +7903,16 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -7923,16 +7923,16 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349">
@@ -7943,16 +7943,16 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350">
@@ -7963,16 +7963,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="351">
@@ -7988,11 +7988,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="352">
@@ -8008,11 +8008,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353">
@@ -8028,11 +8028,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -8043,16 +8043,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -8063,16 +8063,16 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -8083,16 +8083,16 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="357">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -8123,16 +8123,16 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="359">
@@ -8148,11 +8148,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="360">
@@ -8163,16 +8163,16 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
     </row>
     <row r="361">
@@ -8183,16 +8183,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -8203,16 +8203,16 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363">
@@ -8223,16 +8223,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364">
@@ -8248,11 +8248,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="365">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="369">
@@ -8343,16 +8343,16 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="370">
@@ -8363,16 +8363,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="372">
@@ -8403,16 +8403,16 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="373">
@@ -8428,11 +8428,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="374">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="379">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="380">
@@ -8563,16 +8563,16 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="381">
@@ -8583,16 +8583,16 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="382">
@@ -8603,16 +8603,16 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -8643,16 +8643,16 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D386" t="n">
@@ -8708,11 +8708,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -8723,16 +8723,16 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D389" t="n">
@@ -8763,16 +8763,16 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391">
@@ -8783,16 +8783,16 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="392">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="393">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D393" t="n">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -8888,11 +8888,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
@@ -8923,16 +8923,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="399">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="400">
@@ -8963,16 +8963,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="402">
@@ -9003,16 +9003,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="403">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -9048,22 +9048,22 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -9072,18 +9072,18 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -9098,41 +9098,41 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="409">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D409" t="n">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D411" t="n">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -9243,16 +9243,16 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="415">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="420">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9383,12 +9383,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D421" t="n">
@@ -9403,16 +9403,16 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -9423,16 +9423,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="424">
@@ -9448,11 +9448,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="425">
@@ -9468,11 +9468,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="426">
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="429">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="430">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="431">
@@ -9583,16 +9583,16 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -9603,16 +9603,16 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="433">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="437">
@@ -9703,16 +9703,16 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D438" t="n">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="440">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442">
@@ -9808,11 +9808,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443">
@@ -9823,16 +9823,16 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="445">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -9983,16 +9983,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="452">
@@ -10008,11 +10008,11 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="453">
@@ -10028,11 +10028,11 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="454">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -10068,111 +10068,111 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="461">
@@ -10188,11 +10188,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="462">
@@ -10208,11 +10208,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="463">
@@ -10228,11 +10228,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>115</v>
+        <v>4</v>
       </c>
     </row>
     <row r="465">
@@ -10263,16 +10263,16 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="466">
@@ -10283,16 +10283,16 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="469">
@@ -10343,16 +10343,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="470">
@@ -10368,11 +10368,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="471">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D471" t="n">
@@ -10408,11 +10408,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="473">
@@ -10423,16 +10423,16 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -10443,16 +10443,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="475">
@@ -10463,16 +10463,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="476">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D476" t="n">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="478">
@@ -10528,11 +10528,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="479">
@@ -10548,11 +10548,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -10583,16 +10583,16 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -10603,16 +10603,16 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="483">
@@ -10623,16 +10623,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="484">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="485">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="486">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487">
@@ -10708,11 +10708,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="488">
@@ -10728,11 +10728,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489">
@@ -10748,11 +10748,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="490">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="491">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="492">
@@ -10803,16 +10803,16 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="493">
@@ -10823,16 +10823,16 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -10843,16 +10843,16 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="495">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="496">
@@ -10888,11 +10888,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497">
@@ -10908,11 +10908,11 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="498">
@@ -10928,11 +10928,11 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -11063,16 +11063,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -11083,16 +11083,16 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D507" t="n">
@@ -11123,12 +11123,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D508" t="n">
@@ -11143,16 +11143,16 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="510">
@@ -11168,11 +11168,11 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="511">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513">
@@ -11223,16 +11223,16 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -11243,16 +11243,16 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="515">
@@ -11263,16 +11263,16 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="516">
@@ -11283,16 +11283,16 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="518">
@@ -11328,11 +11328,11 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="520">
@@ -11363,16 +11363,16 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="521">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D521" t="n">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="523">
@@ -11423,16 +11423,16 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="524">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -11452,7 +11452,7 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="525">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526">
@@ -11483,16 +11483,16 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="530">
@@ -11568,11 +11568,11 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="531">
@@ -11588,10 +11588,150 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
+          <t>Faceless</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D531" t="n">
+      <c r="D538" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -793,10 +793,10 @@
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -889,7 +889,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D12" t="n">
         <v>72</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="L12" t="n">
-        <v>1015</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="13">
@@ -929,7 +929,7 @@
         <v>5353</v>
       </c>
       <c r="C13" t="n">
-        <v>2673</v>
+        <v>2678</v>
       </c>
       <c r="D13" t="n">
         <v>1221</v>
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>742</v>
+        <v>801</v>
       </c>
       <c r="L13" t="n">
-        <v>13241</v>
+        <v>13305</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D538"/>
+  <dimension ref="A1:D547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="166">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="171">
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="192">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="202">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="207">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="208">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="209">
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="234">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="236">
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="241">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268">
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="269">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="277">
@@ -6703,16 +6703,16 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -6728,11 +6728,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -6808,11 +6808,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -6823,16 +6823,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
@@ -6843,16 +6843,16 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -6903,16 +6903,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -6923,16 +6923,16 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="299">
@@ -6948,11 +6948,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="300">
@@ -6968,11 +6968,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -7008,47 +7008,47 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>268</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>69</v>
+        <v>268</v>
       </c>
     </row>
     <row r="306">
@@ -7088,11 +7088,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="308">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -7148,11 +7148,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>151</v>
+        <v>12</v>
       </c>
     </row>
     <row r="310">
@@ -7168,11 +7168,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>5</v>
+        <v>151</v>
       </c>
     </row>
     <row r="312">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="313">
@@ -7223,16 +7223,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="314">
@@ -7243,16 +7243,16 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="315">
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
     </row>
     <row r="316">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="320">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
@@ -7403,16 +7403,16 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -7423,16 +7423,16 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="324">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="325">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D325" t="n">
@@ -7483,16 +7483,16 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -7563,32 +7563,32 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D331" t="n">
@@ -7598,21 +7598,21 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -7623,16 +7623,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -7683,16 +7683,16 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -7708,11 +7708,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D338" t="n">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
@@ -7763,16 +7763,16 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -7783,27 +7783,27 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7812,23 +7812,23 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -7838,37 +7838,37 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D345" t="n">
@@ -7878,61 +7878,61 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -7948,11 +7948,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="350">
@@ -7968,11 +7968,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
@@ -7983,16 +7983,16 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="352">
@@ -8003,16 +8003,16 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
@@ -8023,16 +8023,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -8043,16 +8043,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -8103,16 +8103,16 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="359">
@@ -8143,16 +8143,16 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="360">
@@ -8163,16 +8163,16 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
@@ -8183,16 +8183,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
@@ -8203,16 +8203,16 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -8223,16 +8223,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="364">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -8263,16 +8263,16 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="366">
@@ -8283,16 +8283,16 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="367">
@@ -8303,16 +8303,16 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="368">
@@ -8323,16 +8323,16 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -8343,16 +8343,16 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
@@ -8363,16 +8363,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -8388,11 +8388,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="372">
@@ -8408,11 +8408,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="374">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375">
@@ -8463,16 +8463,16 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="376">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="377">
@@ -8503,16 +8503,16 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="379">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="380">
@@ -8568,11 +8568,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="381">
@@ -8588,11 +8588,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="382">
@@ -8603,16 +8603,16 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -8643,16 +8643,16 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="385">
@@ -8663,16 +8663,16 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="386">
@@ -8683,16 +8683,16 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="387">
@@ -8703,16 +8703,16 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="388">
@@ -8723,16 +8723,16 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="389">
@@ -8743,16 +8743,16 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="393">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D395" t="n">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -8923,16 +8923,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="399">
@@ -8948,11 +8948,11 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="400">
@@ -8968,11 +8968,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401">
@@ -8988,11 +8988,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="402">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -9043,16 +9043,16 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="407">
@@ -9103,16 +9103,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="408">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -9132,147 +9132,147 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="417">
@@ -9303,12 +9303,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D417" t="n">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419">
@@ -9343,16 +9343,16 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -9363,16 +9363,16 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
@@ -9383,16 +9383,16 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="422">
@@ -9403,16 +9403,16 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423">
@@ -9423,16 +9423,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="426">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="427">
@@ -9503,16 +9503,16 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -9563,16 +9563,16 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="431">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="432">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="433">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="437">
@@ -9703,16 +9703,16 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="438">
@@ -9723,16 +9723,16 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="439">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="440">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="441">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="442">
@@ -9803,16 +9803,16 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="443">
@@ -9823,16 +9823,16 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="445">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -9908,11 +9908,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -9983,16 +9983,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -10003,16 +10003,16 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -10023,16 +10023,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -10043,16 +10043,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="455">
@@ -10063,16 +10063,16 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -10083,16 +10083,16 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -10103,16 +10103,16 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -10123,16 +10123,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="459">
@@ -10148,11 +10148,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="460">
@@ -10168,151 +10168,151 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="468">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="469">
@@ -10348,11 +10348,11 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>115</v>
+        <v>20</v>
       </c>
     </row>
     <row r="470">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="471">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D471" t="n">
@@ -10403,16 +10403,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="473">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="474">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="475">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="476">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>17</v>
+        <v>115</v>
       </c>
     </row>
     <row r="478">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="481">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485">
@@ -10663,16 +10663,16 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="486">
@@ -10683,16 +10683,16 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="487">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -10712,7 +10712,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="491">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="492">
@@ -10803,16 +10803,16 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -10863,16 +10863,16 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="496">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="500">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="503">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="504">
@@ -11043,16 +11043,16 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="506">
@@ -11083,16 +11083,16 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="507">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D507" t="n">
@@ -11123,16 +11123,16 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="509">
@@ -11143,16 +11143,16 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="510">
@@ -11163,12 +11163,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D510" t="n">
@@ -11183,16 +11183,16 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="513">
@@ -11223,16 +11223,16 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="514">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="D515" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516">
@@ -11283,16 +11283,16 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517">
@@ -11303,16 +11303,16 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="518">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="519">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="520">
@@ -11363,16 +11363,16 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="523">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -11432,7 +11432,7 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -11452,7 +11452,7 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="525">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="526">
@@ -11483,12 +11483,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D526" t="n">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530">
@@ -11563,16 +11563,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="531">
@@ -11583,16 +11583,16 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="532">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D532" t="n">
@@ -11623,16 +11623,16 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="534">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -11692,7 +11692,7 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="537">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -11723,15 +11723,195 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
         <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D538" t="n">
+      <c r="D547" t="n">
         <v>11</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -793,10 +793,10 @@
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -886,13 +886,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="L12" t="n">
-        <v>1075</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="13">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5353</v>
+        <v>5354</v>
       </c>
       <c r="C13" t="n">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="D13" t="n">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="E13" t="n">
         <v>301</v>
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>801</v>
+        <v>819</v>
       </c>
       <c r="L13" t="n">
-        <v>13305</v>
+        <v>13326</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D547"/>
+  <dimension ref="A1:D551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="166">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="171">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172">
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="206">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="209">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="217">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="243">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -6148,11 +6148,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -6183,16 +6183,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -6223,16 +6223,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -6323,16 +6323,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -6343,16 +6343,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="270">
@@ -6368,11 +6368,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="271">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6488,11 +6488,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="277">
@@ -6503,16 +6503,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278">
@@ -6523,16 +6523,16 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="279">
@@ -6548,11 +6548,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -6623,16 +6623,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -6643,16 +6643,16 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
@@ -6668,11 +6668,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286">
@@ -6688,11 +6688,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -6723,16 +6723,16 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -6768,11 +6768,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -6848,11 +6848,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -6863,16 +6863,16 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
@@ -6883,16 +6883,16 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -6943,16 +6943,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -6963,16 +6963,16 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="301">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="302">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D303" t="n">
@@ -7048,47 +7048,47 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>268</v>
+        <v>4</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>69</v>
+        <v>268</v>
       </c>
     </row>
     <row r="308">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309">
@@ -7148,11 +7148,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="310">
@@ -7168,11 +7168,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>151</v>
+        <v>12</v>
       </c>
     </row>
     <row r="312">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="313">
@@ -7228,11 +7228,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>5</v>
+        <v>151</v>
       </c>
     </row>
     <row r="314">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="315">
@@ -7263,16 +7263,16 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="316">
@@ -7283,16 +7283,16 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="317">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="320">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="323">
@@ -7428,11 +7428,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324">
@@ -7443,16 +7443,16 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -7463,16 +7463,16 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="326">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D327" t="n">
@@ -7523,16 +7523,16 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D330" t="n">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -7603,56 +7603,56 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -7683,16 +7683,16 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D337" t="n">
@@ -7723,16 +7723,16 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D339" t="n">
@@ -7768,11 +7768,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -7788,11 +7788,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -7803,16 +7803,16 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -7823,16 +7823,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -7863,16 +7863,16 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D346" t="n">
@@ -7903,16 +7903,16 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -7938,12 +7938,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -7952,23 +7952,23 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -7978,21 +7978,21 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
@@ -8008,11 +8008,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="353">
@@ -8028,11 +8028,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -8068,11 +8068,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -8088,11 +8088,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -8108,11 +8108,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -8123,16 +8123,16 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -8143,16 +8143,16 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="360">
@@ -8163,16 +8163,16 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="361">
@@ -8188,11 +8188,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="362">
@@ -8208,11 +8208,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="363">
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -8248,11 +8248,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -8283,16 +8283,16 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="367">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -8323,16 +8323,16 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="370">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="377">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="378">
@@ -8528,11 +8528,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="379">
@@ -8548,11 +8548,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="380">
@@ -8563,16 +8563,16 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="381">
@@ -8583,16 +8583,16 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="382">
@@ -8603,16 +8603,16 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="383">
@@ -8628,11 +8628,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -8708,11 +8708,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="388">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="389">
@@ -8743,16 +8743,16 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="390">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="392">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D393" t="n">
@@ -8843,16 +8843,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="402">
@@ -9008,11 +9008,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="403">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404">
@@ -9048,11 +9048,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="405">
@@ -9068,11 +9068,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -9088,11 +9088,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="409">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="410">
@@ -9163,16 +9163,16 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="411">
@@ -9183,16 +9183,16 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="412">
@@ -9203,16 +9203,16 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="415">
@@ -9268,71 +9268,71 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="419">
@@ -9343,16 +9343,16 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D422" t="n">
@@ -9423,16 +9423,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="425">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D425" t="n">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D427" t="n">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -9548,11 +9548,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="430">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -9583,16 +9583,16 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -9603,16 +9603,16 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="435">
@@ -9668,11 +9668,11 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="436">
@@ -9688,11 +9688,11 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="437">
@@ -9708,11 +9708,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="439">
@@ -9748,11 +9748,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440">
@@ -9763,16 +9763,16 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="441">
@@ -9783,16 +9783,16 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="442">
@@ -9803,16 +9803,16 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="443">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="444">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="449">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -9963,16 +9963,16 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -9988,11 +9988,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="452">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -10028,11 +10028,11 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -10048,11 +10048,11 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D455" t="n">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="459">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -10163,16 +10163,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D461" t="n">
@@ -10203,16 +10203,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="463">
@@ -10228,11 +10228,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D466" t="n">
@@ -10308,91 +10308,91 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472">
@@ -10403,16 +10403,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -10488,11 +10488,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="477">
@@ -10508,11 +10508,11 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>115</v>
+        <v>13</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -10583,16 +10583,16 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
     </row>
     <row r="482">
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="483">
@@ -10628,11 +10628,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
@@ -10648,11 +10648,11 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="485">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486">
@@ -10683,16 +10683,16 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="487">
@@ -10703,12 +10703,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D487" t="n">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="490">
@@ -10768,11 +10768,11 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="491">
@@ -10788,11 +10788,11 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -10823,16 +10823,16 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -10843,16 +10843,16 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="495">
@@ -10863,16 +10863,16 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="496">
@@ -10883,16 +10883,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="497">
@@ -10908,11 +10908,11 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="498">
@@ -10928,11 +10928,11 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -10948,11 +10948,11 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="500">
@@ -10968,11 +10968,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501">
@@ -10988,11 +10988,11 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="502">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="504">
@@ -11043,16 +11043,16 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="505">
@@ -11063,16 +11063,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="506">
@@ -11083,16 +11083,16 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="507">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="508">
@@ -11128,11 +11128,11 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="510">
@@ -11168,11 +11168,11 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="511">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="513">
@@ -11223,16 +11223,16 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="514">
@@ -11243,16 +11243,16 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="515">
@@ -11263,16 +11263,16 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
@@ -11343,16 +11343,16 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="520">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D520" t="n">
@@ -11383,16 +11383,16 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="522">
@@ -11408,11 +11408,11 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="525">
@@ -11463,16 +11463,16 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526">
@@ -11483,16 +11483,16 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="527">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="529">
@@ -11548,11 +11548,11 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="530">
@@ -11568,11 +11568,11 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D531" t="n">
@@ -11608,11 +11608,11 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="533">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="536">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D536" t="n">
@@ -11703,16 +11703,16 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="538">
@@ -11728,11 +11728,11 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539">
@@ -11743,16 +11743,16 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -11763,16 +11763,16 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -11803,16 +11803,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="543">
@@ -11828,11 +11828,11 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="544">
@@ -11848,11 +11848,11 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -11868,11 +11868,11 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546">
@@ -11888,11 +11888,11 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="547">
@@ -11908,11 +11908,91 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D547" t="n">
-        <v>11</v>
+      <c r="D551" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -673,10 +673,10 @@
         <v>104</v>
       </c>
       <c r="K6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L6" t="n">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="L7" t="n">
-        <v>1710</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="8">
@@ -753,10 +753,10 @@
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="L12" t="n">
-        <v>1093</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="13">
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>819</v>
+        <v>837</v>
       </c>
       <c r="L13" t="n">
-        <v>13326</v>
+        <v>13344</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D551"/>
+  <dimension ref="A1:D557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88">
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="127">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="171">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="173">
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="182">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="207">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="208">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="209">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="210">
@@ -5368,11 +5368,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
@@ -5408,11 +5408,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223">
@@ -5428,11 +5428,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224">
@@ -5443,16 +5443,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="225">
@@ -5468,11 +5468,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="226">
@@ -5488,11 +5488,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="228">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -5548,11 +5548,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -5608,11 +5608,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233">
@@ -5623,16 +5623,16 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
     </row>
     <row r="234">
@@ -5648,11 +5648,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="235">
@@ -5668,11 +5668,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="237">
@@ -5708,11 +5708,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -5728,11 +5728,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="239">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -5768,11 +5768,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="241">
@@ -5788,11 +5788,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="242">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
     </row>
     <row r="243">
@@ -5823,16 +5823,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
     </row>
     <row r="244">
@@ -5848,11 +5848,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="245">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -5908,11 +5908,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248">
@@ -5923,16 +5923,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -5948,11 +5948,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="250">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6008,11 +6008,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253">
@@ -6028,11 +6028,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="254">
@@ -6048,11 +6048,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="255">
@@ -6068,11 +6068,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="256">
@@ -6088,31 +6088,31 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="258">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -6168,11 +6168,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -6203,16 +6203,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -6243,16 +6243,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="266">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="271">
@@ -6388,11 +6388,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="272">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -6488,11 +6488,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277">
@@ -6508,11 +6508,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="278">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="279">
@@ -6543,16 +6543,16 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="280">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -6663,16 +6663,16 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">
@@ -6688,11 +6688,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -6728,11 +6728,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6763,16 +6763,16 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -6808,11 +6808,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -6903,16 +6903,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -6943,16 +6943,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="300">
@@ -6968,11 +6968,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -6983,16 +6983,16 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D302" t="n">
@@ -7023,16 +7023,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -7088,71 +7088,71 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>268</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310">
@@ -7168,11 +7168,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>268</v>
       </c>
     </row>
     <row r="311">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="313">
@@ -7228,11 +7228,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="315">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D315" t="n">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>34</v>
+        <v>151</v>
       </c>
     </row>
     <row r="317">
@@ -7303,16 +7303,16 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="318">
@@ -7323,16 +7323,16 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319">
@@ -7343,16 +7343,16 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="320">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="323">
@@ -7428,11 +7428,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324">
@@ -7448,11 +7448,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="326">
@@ -7483,16 +7483,16 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D327" t="n">
@@ -7523,16 +7523,16 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="329">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="330">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D330" t="n">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -7643,52 +7643,52 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -7698,27 +7698,27 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7732,18 +7732,18 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7763,16 +7763,16 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -7823,16 +7823,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -7848,11 +7848,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -7863,16 +7863,16 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D346" t="n">
@@ -7903,16 +7903,16 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349">
@@ -7943,16 +7943,16 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="350">
@@ -7963,16 +7963,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -7998,37 +7998,37 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -8038,37 +8038,37 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -8078,21 +8078,21 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -8108,11 +8108,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
@@ -8148,11 +8148,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="360">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
@@ -8183,16 +8183,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -8203,16 +8203,16 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -8223,16 +8223,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="365">
@@ -8263,16 +8263,16 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="366">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
@@ -8343,16 +8343,16 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="372">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="374">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
     </row>
     <row r="375">
@@ -8463,16 +8463,16 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -8503,16 +8503,16 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379">
@@ -8548,11 +8548,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="380">
@@ -8568,11 +8568,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -8588,11 +8588,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="382">
@@ -8608,11 +8608,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="384">
@@ -8643,16 +8643,16 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="385">
@@ -8663,16 +8663,16 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="386">
@@ -8683,16 +8683,16 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="387">
@@ -8703,16 +8703,16 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="388">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="392">
@@ -8803,16 +8803,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="394">
@@ -8843,16 +8843,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="395">
@@ -8863,16 +8863,16 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="397">
@@ -8903,16 +8903,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -8923,16 +8923,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -8968,11 +8968,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="401">
@@ -8988,11 +8988,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402">
@@ -9003,16 +9003,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="403">
@@ -9023,16 +9023,16 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
@@ -9043,16 +9043,16 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D409" t="n">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -9203,16 +9203,16 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="414">
@@ -9243,16 +9243,16 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9332,38 +9332,38 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -9372,18 +9372,18 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -9398,41 +9398,41 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="425">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D426" t="n">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="428">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="429">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="430">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -9623,16 +9623,16 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D434" t="n">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D437" t="n">
@@ -9723,16 +9723,16 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="442">
@@ -9808,11 +9808,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443">
@@ -9828,11 +9828,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="446">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="449">
@@ -9943,16 +9943,16 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -9963,16 +9963,16 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -9983,16 +9983,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -10003,16 +10003,16 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="453">
@@ -10023,16 +10023,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="454">
@@ -10043,12 +10043,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -10063,16 +10063,16 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -10083,16 +10083,16 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="457">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="458">
@@ -10128,11 +10128,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D460" t="n">
@@ -10183,16 +10183,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -10203,16 +10203,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
@@ -10223,16 +10223,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -10243,16 +10243,16 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="465">
@@ -10263,16 +10263,16 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -10283,12 +10283,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D466" t="n">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="469">
@@ -10348,11 +10348,11 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="470">
@@ -10368,11 +10368,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="471">
@@ -10388,131 +10388,131 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="479">
@@ -10548,11 +10548,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="480">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="481">
@@ -10588,11 +10588,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D482" t="n">
@@ -10623,16 +10623,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="484">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="485">
@@ -10663,16 +10663,16 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="486">
@@ -10683,16 +10683,16 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487">
@@ -10703,16 +10703,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="488">
@@ -10728,11 +10728,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="489">
@@ -10748,11 +10748,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
@@ -10803,16 +10803,16 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="493">
@@ -10823,16 +10823,16 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="494">
@@ -10843,16 +10843,16 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -10863,16 +10863,16 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="496">
@@ -10888,11 +10888,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="498">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="503">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="506">
@@ -11088,11 +11088,11 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -11103,16 +11103,16 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="508">
@@ -11123,16 +11123,16 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="509">
@@ -11143,16 +11143,16 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="510">
@@ -11163,16 +11163,16 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="511">
@@ -11183,16 +11183,16 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="513">
@@ -11228,11 +11228,11 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="514">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="516">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D516" t="n">
@@ -11303,16 +11303,16 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="518">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -11332,7 +11332,7 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="519">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="520">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -11372,7 +11372,7 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="521">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="522">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="523">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -11432,7 +11432,7 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D524" t="n">
@@ -11463,12 +11463,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -11483,16 +11483,16 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="528">
@@ -11528,11 +11528,11 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="530">
@@ -11563,16 +11563,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="531">
@@ -11583,16 +11583,16 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532">
@@ -11603,12 +11603,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D532" t="n">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D533" t="n">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="535">
@@ -11668,11 +11668,11 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="536">
@@ -11688,11 +11688,11 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -11708,11 +11708,11 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="538">
@@ -11723,16 +11723,16 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="539">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D539" t="n">
@@ -11763,16 +11763,16 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="541">
@@ -11783,16 +11783,16 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="542">
@@ -11803,16 +11803,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
@@ -11823,16 +11823,16 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
@@ -11863,16 +11863,16 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="546">
@@ -11883,16 +11883,16 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
@@ -11903,16 +11903,16 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="548">
@@ -11923,16 +11923,16 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="549">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="550">
@@ -11968,11 +11968,11 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -11988,10 +11988,130 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D551" t="n">
+      <c r="D557" t="n">
         <v>12</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -793,10 +793,10 @@
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L9" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="n">
         <v>355</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="L12" t="n">
-        <v>1099</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="13">
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5354</v>
+        <v>5355</v>
       </c>
       <c r="C13" t="n">
         <v>2679</v>
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>837</v>
+        <v>861</v>
       </c>
       <c r="L13" t="n">
-        <v>13344</v>
+        <v>13369</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D557"/>
+  <dimension ref="A1:D558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="167">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="171">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="202">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="204">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="207">
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="242">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="245">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266">
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="280">
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="310">
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="341">
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347">
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="425">
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="439">
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="446">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="479">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="505">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -11088,11 +11088,11 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="507">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -11128,11 +11128,11 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="509">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="510">
@@ -11168,11 +11168,11 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="511">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="512">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="513">
@@ -11223,16 +11223,16 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="514">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="518">
@@ -11328,11 +11328,11 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="521">
@@ -11388,11 +11388,11 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
@@ -11508,11 +11508,11 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="529">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D529" t="n">
@@ -11568,11 +11568,11 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="531">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D531" t="n">
@@ -11608,11 +11608,11 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="533">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="534">
@@ -11648,11 +11648,11 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="536">
@@ -11688,11 +11688,11 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="537">
@@ -11708,11 +11708,11 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -11728,11 +11728,11 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="539">
@@ -11748,11 +11748,11 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="540">
@@ -11768,11 +11768,11 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -11808,11 +11808,11 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="543">
@@ -11828,11 +11828,11 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="545">
@@ -11868,11 +11868,11 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546">
@@ -11888,11 +11888,11 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="547">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D547" t="n">
@@ -11928,11 +11928,11 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
@@ -11943,16 +11943,16 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="550">
@@ -11968,11 +11968,11 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="551">
@@ -11988,11 +11988,11 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552">
@@ -12008,11 +12008,11 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -12028,11 +12028,11 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -12048,11 +12048,11 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="555">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D555" t="n">
@@ -12088,11 +12088,11 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="557">
@@ -12108,10 +12108,30 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D557" t="n">
+      <c r="D558" t="n">
         <v>12</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -513,10 +513,10 @@
         <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L2" t="n">
-        <v>5656</v>
+        <v>5658</v>
       </c>
     </row>
     <row r="3">
@@ -633,10 +633,10 @@
         <v>143</v>
       </c>
       <c r="K5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L5" t="n">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="6">
@@ -652,7 +652,7 @@
         <v>239</v>
       </c>
       <c r="D6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E6" t="n">
         <v>31</v>
@@ -673,10 +673,10 @@
         <v>104</v>
       </c>
       <c r="K6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L6" t="n">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="7">
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C7" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D7" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E7" t="n">
         <v>49</v>
@@ -713,10 +713,10 @@
         <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="L7" t="n">
-        <v>1718</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="8">
@@ -726,19 +726,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -753,7 +753,7 @@
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L8" t="n">
         <v>355</v>
@@ -766,19 +766,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" t="n">
         <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -793,10 +793,10 @@
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>26</v>
@@ -827,16 +827,16 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="L12" t="n">
-        <v>1122</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="13">
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D558"/>
+  <dimension ref="A1:D557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58">
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="80">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="87">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="89">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="126">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="135">
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="142">
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="144">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="171">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="181">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="200">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="207">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="208">
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="243">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="250">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="254">
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="256">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="258">
@@ -6123,16 +6123,16 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -6168,11 +6168,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="261">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -6203,16 +6203,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -6243,16 +6243,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="265">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="271">
@@ -6388,11 +6388,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6488,11 +6488,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="277">
@@ -6508,11 +6508,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="279">
@@ -6543,16 +6543,16 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -6628,11 +6628,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285">
@@ -6663,16 +6663,16 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286">
@@ -6688,11 +6688,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -6763,16 +6763,16 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -6783,16 +6783,16 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292">
@@ -6808,11 +6808,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="299">
@@ -6943,16 +6943,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -6968,11 +6968,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303">
@@ -7023,16 +7023,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="308">
@@ -7128,31 +7128,31 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>6</v>
+        <v>268</v>
       </c>
     </row>
     <row r="310">
@@ -7168,11 +7168,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>268</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="312">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -7228,11 +7228,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="314">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315">
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>5</v>
+        <v>151</v>
       </c>
     </row>
     <row r="316">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>151</v>
+        <v>46</v>
       </c>
     </row>
     <row r="317">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="319">
@@ -7343,16 +7343,16 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="320">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -7448,11 +7448,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="325">
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="328">
@@ -7523,16 +7523,16 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="329">
@@ -7548,11 +7548,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -7623,16 +7623,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -7648,11 +7648,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -7688,31 +7688,31 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D338" t="n">
@@ -7738,21 +7738,21 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -7823,16 +7823,16 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D344" t="n">
@@ -7868,11 +7868,11 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -7888,11 +7888,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348">
@@ -7928,11 +7928,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -7963,16 +7963,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
@@ -7988,11 +7988,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352">
@@ -8003,16 +8003,16 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
@@ -8023,12 +8023,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -8068,31 +8068,31 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="357">
@@ -8108,11 +8108,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="359">
@@ -8148,11 +8148,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="361">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -8208,11 +8208,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="364">
@@ -8248,11 +8248,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="365">
@@ -8263,16 +8263,16 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="366">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="371">
@@ -8388,11 +8388,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -8408,11 +8408,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="373">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="374">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="379">
@@ -8548,11 +8548,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -8568,11 +8568,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="381">
@@ -8588,11 +8588,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="382">
@@ -8608,11 +8608,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="383">
@@ -8628,11 +8628,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="386">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="387">
@@ -8703,16 +8703,16 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="388">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="392">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="393">
@@ -8828,11 +8828,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="394">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="396">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400">
@@ -8968,11 +8968,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401">
@@ -8988,11 +8988,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="402">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -9068,11 +9068,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="413">
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="415">
@@ -9268,11 +9268,11 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -9308,11 +9308,11 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -9408,31 +9408,31 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D425" t="n">
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -9528,11 +9528,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="429">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D431" t="n">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -9623,16 +9623,16 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="434">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D436" t="n">
@@ -9708,11 +9708,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="439">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="440">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442">
@@ -9808,11 +9808,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="443">
@@ -9828,11 +9828,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="444">
@@ -9848,11 +9848,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="445">
@@ -9868,11 +9868,11 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="446">
@@ -9888,11 +9888,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="447">
@@ -9908,11 +9908,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -9988,11 +9988,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -10352,7 +10352,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="470">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="476">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="478">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="479">
@@ -10948,11 +10948,11 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="500">
@@ -10968,11 +10968,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="501">
@@ -10988,11 +10988,11 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="506">
@@ -11088,11 +11088,11 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="508">
@@ -11128,11 +11128,11 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="509">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="510">
@@ -11168,11 +11168,11 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="511">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="512">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="513">
@@ -11223,16 +11223,16 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
     </row>
     <row r="514">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="518">
@@ -11328,11 +11328,11 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="521">
@@ -11388,11 +11388,11 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="525">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
@@ -11508,11 +11508,11 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="529">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D529" t="n">
@@ -11568,11 +11568,11 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="531">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D531" t="n">
@@ -11608,11 +11608,11 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="533">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -11648,11 +11648,11 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="536">
@@ -11688,11 +11688,11 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -11708,11 +11708,11 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="538">
@@ -11728,11 +11728,11 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="539">
@@ -11748,11 +11748,11 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -11768,11 +11768,11 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="541">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -11808,11 +11808,11 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
@@ -11828,11 +11828,11 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
@@ -11868,11 +11868,11 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="546">
@@ -11888,11 +11888,11 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D547" t="n">
@@ -11928,11 +11928,11 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="549">
@@ -11943,16 +11943,16 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="550">
@@ -11968,11 +11968,11 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -11988,11 +11988,11 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552">
@@ -12008,11 +12008,11 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -12028,11 +12028,11 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="554">
@@ -12048,11 +12048,11 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="555">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D555" t="n">
@@ -12088,11 +12088,11 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="557">
@@ -12108,30 +12108,10 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
-      <c r="D558" t="n">
         <v>12</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -513,10 +513,10 @@
         <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L2" t="n">
-        <v>5658</v>
+        <v>5656</v>
       </c>
     </row>
     <row r="3">
@@ -713,10 +713,10 @@
         <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L7" t="n">
-        <v>1727</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="8">
@@ -753,10 +753,10 @@
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L8" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -793,10 +793,10 @@
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L12" t="n">
-        <v>1107</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="13">
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="L13" t="n">
-        <v>13369</v>
+        <v>13380</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D557"/>
+  <dimension ref="A1:D561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88">
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="171">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="181">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="183">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="202">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="207">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="208">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="209">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="242">
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="256">
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="257">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="271">
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -7128,31 +7128,31 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>268</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310">
@@ -7168,11 +7168,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>5</v>
+        <v>268</v>
       </c>
     </row>
     <row r="311">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="313">
@@ -7228,11 +7228,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="315">
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>151</v>
+        <v>5</v>
       </c>
     </row>
     <row r="316">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>46</v>
+        <v>151</v>
       </c>
     </row>
     <row r="317">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319">
@@ -7343,16 +7343,16 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
     </row>
     <row r="320">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="323">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -7448,11 +7448,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="326">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -7523,16 +7523,16 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="329">
@@ -7548,11 +7548,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="330">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -7623,16 +7623,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -7648,11 +7648,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -7688,31 +7688,31 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="338">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D338" t="n">
@@ -7738,32 +7738,32 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7778,17 +7778,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -7803,16 +7803,16 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D344" t="n">
@@ -7863,16 +7863,16 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -7888,11 +7888,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -7943,16 +7943,16 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
@@ -7963,16 +7963,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="351">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
@@ -8003,16 +8003,16 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="353">
@@ -8023,12 +8023,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -8043,12 +8043,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8072,43 +8072,43 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -8118,41 +8118,41 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="361">
@@ -8188,11 +8188,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -8208,11 +8208,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -8248,11 +8248,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -8263,16 +8263,16 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -8283,16 +8283,16 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -8303,16 +8303,16 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="368">
@@ -8323,16 +8323,16 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="370">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="371">
@@ -8388,11 +8388,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372">
@@ -8408,11 +8408,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="375">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="377">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -8563,16 +8563,16 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
@@ -8583,16 +8583,16 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -8608,11 +8608,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="383">
@@ -8628,11 +8628,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="387">
@@ -8703,16 +8703,16 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="388">
@@ -8723,16 +8723,16 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="389">
@@ -8743,16 +8743,16 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="390">
@@ -8763,16 +8763,16 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="391">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="392">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="393">
@@ -8828,11 +8828,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="396">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="397">
@@ -8903,16 +8903,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="398">
@@ -8923,16 +8923,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="400">
@@ -8963,16 +8963,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402">
@@ -9003,16 +9003,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -9068,11 +9068,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D407" t="n">
@@ -9123,16 +9123,16 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="411">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D411" t="n">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="413">
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -9268,11 +9268,11 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="418">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="419">
@@ -9343,16 +9343,16 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="420">
@@ -9363,16 +9363,16 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -9383,12 +9383,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D421" t="n">
@@ -9408,47 +9408,47 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -9458,41 +9458,41 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="427">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="428">
@@ -9528,11 +9528,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -9563,16 +9563,16 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -9583,16 +9583,16 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="433">
@@ -9623,16 +9623,16 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D434" t="n">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -9708,11 +9708,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="438">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440">
@@ -9763,16 +9763,16 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
@@ -9783,16 +9783,16 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="442">
@@ -9803,16 +9803,16 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="443">
@@ -9828,11 +9828,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="444">
@@ -9848,11 +9848,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="445">
@@ -9868,11 +9868,11 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
@@ -9888,11 +9888,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="447">
@@ -9908,11 +9908,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="449">
@@ -9943,16 +9943,16 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="450">
@@ -9963,16 +9963,16 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="451">
@@ -9983,16 +9983,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="452">
@@ -10008,11 +10008,11 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -10023,16 +10023,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10052,7 +10052,7 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="457">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="458">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D458" t="n">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D459" t="n">
@@ -10163,16 +10163,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -10188,11 +10188,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="462">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D462" t="n">
@@ -10228,11 +10228,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
@@ -10263,12 +10263,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -10312,7 +10312,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="468">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="469">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10352,7 +10352,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="470">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D471" t="n">
@@ -10403,16 +10403,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -10488,11 +10488,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
@@ -10508,91 +10508,91 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="482">
@@ -10603,16 +10603,16 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="483">
@@ -10628,11 +10628,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="484">
@@ -10648,11 +10648,11 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="485">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="487">
@@ -10708,11 +10708,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>116</v>
+        <v>13</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="490">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="495">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
@@ -10883,16 +10883,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="497">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="500">
@@ -10968,11 +10968,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="501">
@@ -10988,11 +10988,11 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="502">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="504">
@@ -11043,16 +11043,16 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="505">
@@ -11063,16 +11063,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -11083,16 +11083,16 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="507">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="508">
@@ -11128,11 +11128,11 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="509">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="510">
@@ -11168,11 +11168,11 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="512">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="513">
@@ -11223,16 +11223,16 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="514">
@@ -11243,16 +11243,16 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="515">
@@ -11263,16 +11263,16 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="516">
@@ -11283,16 +11283,16 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="518">
@@ -11328,11 +11328,11 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="521">
@@ -11388,11 +11388,11 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="523">
@@ -11423,16 +11423,16 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="524">
@@ -11443,16 +11443,16 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="525">
@@ -11463,16 +11463,16 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="526">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="527">
@@ -11508,11 +11508,11 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530">
@@ -11563,16 +11563,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -11583,16 +11583,16 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="532">
@@ -11608,11 +11608,11 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="533">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="534">
@@ -11648,11 +11648,11 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536">
@@ -11683,16 +11683,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="537">
@@ -11703,16 +11703,16 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -11723,16 +11723,16 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="539">
@@ -11748,11 +11748,11 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="540">
@@ -11768,11 +11768,11 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -11808,11 +11808,11 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="543">
@@ -11828,11 +11828,11 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="545">
@@ -11863,16 +11863,16 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="546">
@@ -11883,12 +11883,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D546" t="n">
@@ -11903,16 +11903,16 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="548">
@@ -11928,11 +11928,11 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
@@ -11943,16 +11943,16 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="550">
@@ -11963,16 +11963,16 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D551" t="n">
@@ -12003,16 +12003,16 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="553">
@@ -12028,11 +12028,11 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="554">
@@ -12048,11 +12048,11 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -12068,11 +12068,11 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556">
@@ -12088,11 +12088,11 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -12108,10 +12108,90 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D557" t="n">
+      <c r="D561" t="n">
         <v>12</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -489,7 +489,7 @@
         <v>3071</v>
       </c>
       <c r="C2" t="n">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D2" t="n">
         <v>361</v>
@@ -513,10 +513,10 @@
         <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="L2" t="n">
-        <v>5656</v>
+        <v>5664</v>
       </c>
     </row>
     <row r="3">
@@ -633,10 +633,10 @@
         <v>143</v>
       </c>
       <c r="K5" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L5" t="n">
-        <v>1394</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="6">
@@ -673,10 +673,10 @@
         <v>104</v>
       </c>
       <c r="K6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L6" t="n">
-        <v>1032</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="7">
@@ -689,7 +689,7 @@
         <v>493</v>
       </c>
       <c r="C7" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D7" t="n">
         <v>220</v>
@@ -713,10 +713,10 @@
         <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="L7" t="n">
-        <v>1731</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="8">
@@ -753,10 +753,10 @@
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -793,10 +793,10 @@
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="L9" t="n">
-        <v>313</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -889,10 +889,10 @@
         <v>68</v>
       </c>
       <c r="C12" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
@@ -901,7 +901,7 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="L12" t="n">
-        <v>1111</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="13">
@@ -929,10 +929,10 @@
         <v>5355</v>
       </c>
       <c r="C13" t="n">
-        <v>2679</v>
+        <v>2684</v>
       </c>
       <c r="D13" t="n">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="E13" t="n">
         <v>301</v>
@@ -941,7 +941,7 @@
         <v>414</v>
       </c>
       <c r="G13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H13" t="n">
         <v>128</v>
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>872</v>
+        <v>937</v>
       </c>
       <c r="L13" t="n">
-        <v>13380</v>
+        <v>13452</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D561"/>
+  <dimension ref="A1:D571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="80">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="88">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="127">
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="166">
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167">
@@ -4308,11 +4308,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -4328,11 +4328,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="170">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>171</v>
+        <v>9</v>
       </c>
     </row>
     <row r="171">
@@ -4388,11 +4388,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>9</v>
+        <v>177</v>
       </c>
     </row>
     <row r="172">
@@ -4403,16 +4403,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="173">
@@ -4428,11 +4428,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4468,11 +4468,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4508,11 +4508,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -4548,11 +4548,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180">
@@ -4568,11 +4568,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
     </row>
     <row r="182">
@@ -4603,16 +4603,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
     </row>
     <row r="183">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="184">
@@ -4648,11 +4648,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -4728,11 +4728,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189">
@@ -4748,11 +4748,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190">
@@ -4768,11 +4768,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191">
@@ -4783,16 +4783,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="192">
@@ -4808,11 +4808,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="193">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -4868,11 +4868,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197">
@@ -4908,11 +4908,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198">
@@ -4928,11 +4928,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199">
@@ -4943,16 +4943,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>158</v>
+        <v>14</v>
       </c>
     </row>
     <row r="200">
@@ -4968,11 +4968,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>4</v>
+        <v>164</v>
       </c>
     </row>
     <row r="201">
@@ -4988,11 +4988,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="203">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="205">
@@ -5068,11 +5068,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="206">
@@ -5088,11 +5088,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="207">
@@ -5108,11 +5108,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
     </row>
     <row r="208">
@@ -5128,11 +5128,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>122</v>
+        <v>57</v>
       </c>
     </row>
     <row r="209">
@@ -5143,16 +5143,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>71</v>
+        <v>122</v>
       </c>
     </row>
     <row r="210">
@@ -5168,11 +5168,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="211">
@@ -5188,11 +5188,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -5208,11 +5208,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="213">
@@ -5228,11 +5228,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -5248,11 +5248,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="216">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="217">
@@ -5308,11 +5308,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="218">
@@ -5328,11 +5328,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>91</v>
+        <v>15</v>
       </c>
     </row>
     <row r="219">
@@ -5343,16 +5343,16 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>10</v>
+        <v>91</v>
       </c>
     </row>
     <row r="220">
@@ -5368,11 +5368,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -5408,11 +5408,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -5428,11 +5428,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -5448,11 +5448,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225">
@@ -5463,16 +5463,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226">
@@ -5483,16 +5483,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="227">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -5548,11 +5548,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -5588,11 +5588,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -5608,11 +5608,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234">
@@ -5643,16 +5643,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235">
@@ -5663,16 +5663,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="236">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
     </row>
     <row r="237">
@@ -5708,11 +5708,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -5728,11 +5728,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="239">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -5768,11 +5768,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="241">
@@ -5788,11 +5788,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="243">
@@ -5828,11 +5828,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
     </row>
     <row r="244">
@@ -5843,16 +5843,16 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="245">
@@ -5863,16 +5863,16 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="246">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -5928,11 +5928,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249">
@@ -5943,16 +5943,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="252">
@@ -6008,11 +6008,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="253">
@@ -6028,11 +6028,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -6048,11 +6048,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="255">
@@ -6068,11 +6068,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="256">
@@ -6088,11 +6088,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257">
@@ -6108,51 +6108,51 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="260">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="261">
@@ -6188,11 +6188,11 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6223,16 +6223,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264">
@@ -6243,16 +6243,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="265">
@@ -6263,16 +6263,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -6383,16 +6383,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -6403,16 +6403,16 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273">
@@ -6423,16 +6423,16 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
@@ -6488,11 +6488,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="277">
@@ -6508,11 +6508,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -6543,16 +6543,16 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280">
@@ -6563,16 +6563,16 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="281">
@@ -6583,16 +6583,16 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="282">
@@ -6603,16 +6603,16 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="283">
@@ -6628,11 +6628,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
@@ -6663,16 +6663,16 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -6703,16 +6703,16 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
@@ -6723,16 +6723,16 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="290">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -6783,16 +6783,16 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -6803,16 +6803,16 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -6823,16 +6823,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -6943,16 +6943,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -6972,7 +6972,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7003,16 +7003,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
@@ -7023,16 +7023,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="304">
@@ -7043,16 +7043,16 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7063,16 +7063,16 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -7083,16 +7083,16 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D307" t="n">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="309">
@@ -7148,87 +7148,87 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>268</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D313" t="n">
@@ -7238,21 +7238,21 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="315">
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>5</v>
+        <v>268</v>
       </c>
     </row>
     <row r="316">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>151</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="320">
@@ -7363,16 +7363,16 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="321">
@@ -7383,16 +7383,16 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>151</v>
       </c>
     </row>
     <row r="322">
@@ -7403,16 +7403,16 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="323">
@@ -7423,16 +7423,16 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324">
@@ -7443,16 +7443,16 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="325">
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
     </row>
     <row r="326">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="328">
@@ -7528,11 +7528,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -7543,16 +7543,16 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="331">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D331" t="n">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="334">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="335">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -7703,27 +7703,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7738,12 +7738,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7752,23 +7752,23 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -7778,12 +7778,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7798,17 +7798,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -7818,17 +7818,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -7838,17 +7838,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D344" t="n">
@@ -7858,17 +7858,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D345" t="n">
@@ -7878,7 +7878,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -7888,27 +7888,27 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D347" t="n">
@@ -7918,32 +7918,32 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -7972,7 +7972,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
@@ -7983,16 +7983,16 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
@@ -8003,16 +8003,16 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
@@ -8023,16 +8023,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354">
@@ -8043,16 +8043,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -8063,16 +8063,16 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -8103,16 +8103,16 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="358">
@@ -8123,16 +8123,16 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -8158,37 +8158,37 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -8198,132 +8198,132 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="370">
@@ -8363,16 +8363,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -8403,16 +8403,16 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="374">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375">
@@ -8463,16 +8463,16 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="376">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="377">
@@ -8503,16 +8503,16 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="379">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D381" t="n">
@@ -8603,16 +8603,16 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="384">
@@ -8643,16 +8643,16 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -8663,16 +8663,16 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="386">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D386" t="n">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="392">
@@ -8803,16 +8803,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="394">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="396">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="397">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="398">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="399">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="400">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="402">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -9043,16 +9043,16 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="405">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="407">
@@ -9103,16 +9103,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="408">
@@ -9123,16 +9123,16 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="409">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -9163,16 +9163,16 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D411" t="n">
@@ -9203,16 +9203,16 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -9243,16 +9243,16 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="420">
@@ -9363,16 +9363,16 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9383,16 +9383,16 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="422">
@@ -9403,16 +9403,16 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D423" t="n">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="426">
@@ -9483,27 +9483,27 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -9512,138 +9512,138 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -9652,27 +9652,27 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -9703,16 +9703,16 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D438" t="n">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="440">
@@ -9763,16 +9763,16 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="441">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D441" t="n">
@@ -9803,16 +9803,16 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443">
@@ -9823,16 +9823,16 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -9943,16 +9943,16 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -9963,16 +9963,16 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -9983,16 +9983,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="452">
@@ -10003,16 +10003,16 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="453">
@@ -10023,16 +10023,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="454">
@@ -10043,16 +10043,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="455">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D455" t="n">
@@ -10083,16 +10083,16 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="457">
@@ -10103,16 +10103,16 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="458">
@@ -10123,16 +10123,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="460">
@@ -10163,16 +10163,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="461">
@@ -10183,16 +10183,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="462">
@@ -10203,16 +10203,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -10223,16 +10223,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464">
@@ -10243,16 +10243,16 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -10263,12 +10263,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -10283,16 +10283,16 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -10343,16 +10343,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="472">
@@ -10403,16 +10403,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
@@ -10423,16 +10423,16 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -10443,16 +10443,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -10463,16 +10463,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -10483,16 +10483,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -10583,47 +10583,47 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -10632,18 +10632,18 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -10652,18 +10652,18 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -10678,12 +10678,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -10692,18 +10692,18 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -10712,18 +10712,18 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -10732,18 +10732,18 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -10752,18 +10752,18 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -10772,18 +10772,18 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>116</v>
+        <v>6</v>
       </c>
     </row>
     <row r="492">
@@ -10803,16 +10803,16 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="493">
@@ -10823,16 +10823,16 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="494">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="495">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D495" t="n">
@@ -10883,16 +10883,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="500">
@@ -10963,16 +10963,16 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -11043,16 +11043,16 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="505">
@@ -11063,12 +11063,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D505" t="n">
@@ -11083,16 +11083,16 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="507">
@@ -11103,16 +11103,16 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="508">
@@ -11123,16 +11123,16 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -11143,16 +11143,16 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="510">
@@ -11163,16 +11163,16 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="511">
@@ -11183,16 +11183,16 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="D513" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="514">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="515">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="D515" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="516">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="D516" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
     </row>
     <row r="517">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="518">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -11332,7 +11332,7 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="519">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="520">
@@ -11363,16 +11363,16 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521">
@@ -11383,16 +11383,16 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="523">
@@ -11423,16 +11423,16 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="524">
@@ -11443,16 +11443,16 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="525">
@@ -11463,16 +11463,16 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="526">
@@ -11483,16 +11483,16 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="527">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="528">
@@ -11523,12 +11523,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D528" t="n">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="530">
@@ -11563,16 +11563,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="531">
@@ -11583,16 +11583,16 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532">
@@ -11603,16 +11603,16 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="533">
@@ -11623,16 +11623,16 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="534">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="536">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D536" t="n">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D537" t="n">
@@ -11723,16 +11723,16 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539">
@@ -11743,16 +11743,16 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D540" t="n">
@@ -11783,16 +11783,16 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="542">
@@ -11803,16 +11803,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="543">
@@ -11823,16 +11823,16 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
@@ -11863,16 +11863,16 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546">
@@ -11883,16 +11883,16 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="547">
@@ -11903,16 +11903,16 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="548">
@@ -11923,16 +11923,16 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="549">
@@ -11943,16 +11943,16 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="550">
@@ -11963,16 +11963,16 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="551">
@@ -11983,16 +11983,16 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="552">
@@ -12003,16 +12003,16 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="553">
@@ -12023,16 +12023,16 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -12043,16 +12043,16 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="555">
@@ -12063,16 +12063,16 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="556">
@@ -12083,16 +12083,16 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="557">
@@ -12103,16 +12103,16 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="558">
@@ -12123,16 +12123,16 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559">
@@ -12143,16 +12143,16 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="560">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D560" t="n">
@@ -12183,15 +12183,215 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>White/European</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Faceless</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
         <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D561" t="n">
+      <c r="D571" t="n">
         <v>12</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -673,10 +673,10 @@
         <v>104</v>
       </c>
       <c r="K6" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L6" t="n">
-        <v>1037</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L7" t="n">
-        <v>1771</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="8">
@@ -753,10 +753,10 @@
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="L12" t="n">
-        <v>1100</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="13">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="88">
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="127">
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="172">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="209">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="245">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="282">
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -513,10 +513,10 @@
         <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L2" t="n">
-        <v>5664</v>
+        <v>5666</v>
       </c>
     </row>
     <row r="3">
@@ -593,10 +593,10 @@
         <v>94</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="5">
@@ -633,10 +633,10 @@
         <v>143</v>
       </c>
       <c r="K5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L5" t="n">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="6">
@@ -655,7 +655,7 @@
         <v>124</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
@@ -673,10 +673,10 @@
         <v>104</v>
       </c>
       <c r="K6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L6" t="n">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         <v>202</v>
       </c>
       <c r="K7" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="L7" t="n">
-        <v>1781</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="8">
@@ -753,10 +753,10 @@
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L8" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -793,10 +793,10 @@
         <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="L12" t="n">
-        <v>1084</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="13">
@@ -935,7 +935,7 @@
         <v>1223</v>
       </c>
       <c r="E13" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F13" t="n">
         <v>414</v>
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>937</v>
+        <v>963</v>
       </c>
       <c r="L13" t="n">
-        <v>13452</v>
+        <v>13479</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D571"/>
+  <dimension ref="A1:D576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="172">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="184">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="201">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="203">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="207">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="209">
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="218">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="236">
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="237">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="243">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="246">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="252">
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="258">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -6228,11 +6228,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265">
@@ -6263,16 +6263,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -6303,16 +6303,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -6323,16 +6323,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -6343,16 +6343,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -6368,11 +6368,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271">
@@ -6388,11 +6388,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274">
@@ -6443,16 +6443,16 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -6463,16 +6463,16 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -6483,16 +6483,16 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277">
@@ -6508,11 +6508,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="278">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -6548,11 +6548,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="280">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="281">
@@ -6588,11 +6588,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="282">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="283">
@@ -6623,16 +6623,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="284">
@@ -6643,16 +6643,16 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="285">
@@ -6663,16 +6663,16 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="286">
@@ -6688,11 +6688,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -6728,11 +6728,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -6743,16 +6743,16 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -6763,16 +6763,16 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -6783,16 +6783,16 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="292">
@@ -6808,11 +6808,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293">
@@ -6828,11 +6828,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
@@ -6843,16 +6843,16 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -6863,16 +6863,16 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296">
@@ -6883,16 +6883,16 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297">
@@ -6903,16 +6903,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -6928,11 +6928,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="299">
@@ -6948,11 +6948,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
@@ -7028,11 +7028,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7043,16 +7043,16 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="305">
@@ -7063,16 +7063,16 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -7083,16 +7083,16 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="307">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
@@ -7123,16 +7123,16 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D309" t="n">
@@ -7163,16 +7163,16 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="312">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -7228,11 +7228,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -7248,71 +7248,71 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>268</v>
+        <v>6</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>268</v>
       </c>
     </row>
     <row r="319">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="323">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -7448,11 +7448,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>34</v>
+        <v>151</v>
       </c>
     </row>
     <row r="325">
@@ -7463,16 +7463,16 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="326">
@@ -7483,16 +7483,16 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327">
@@ -7503,16 +7503,16 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="328">
@@ -7528,11 +7528,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="329">
@@ -7548,11 +7548,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -7568,11 +7568,11 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331">
@@ -7588,11 +7588,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -7608,11 +7608,11 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="334">
@@ -7643,16 +7643,16 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -7683,16 +7683,16 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="337">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="338">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D338" t="n">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -7803,32 +7803,32 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -7838,12 +7838,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7858,12 +7858,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D346" t="n">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D347" t="n">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -7958,17 +7958,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -7978,17 +7978,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -7998,17 +7998,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -8023,16 +8023,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -8043,16 +8043,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -8063,16 +8063,16 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -8108,11 +8108,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8183,16 +8183,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="362">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D362" t="n">
@@ -8223,16 +8223,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -8303,16 +8303,16 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="368">
@@ -8323,27 +8323,27 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8352,23 +8352,23 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -8378,41 +8378,41 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -8428,11 +8428,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="374">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380">
@@ -8563,16 +8563,16 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="381">
@@ -8583,16 +8583,16 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="382">
@@ -8608,11 +8608,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="383">
@@ -8628,11 +8628,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -8683,16 +8683,16 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -8703,16 +8703,16 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="388">
@@ -8723,16 +8723,16 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="389">
@@ -8743,16 +8743,16 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="391">
@@ -8783,16 +8783,16 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="392">
@@ -8803,16 +8803,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="394">
@@ -8843,16 +8843,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="396">
@@ -8888,11 +8888,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="398">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399">
@@ -8948,11 +8948,11 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="400">
@@ -8963,16 +8963,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="402">
@@ -9003,16 +9003,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="403">
@@ -9023,16 +9023,16 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="404">
@@ -9048,11 +9048,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="405">
@@ -9068,11 +9068,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="406">
@@ -9088,11 +9088,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="409">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="410">
@@ -9163,16 +9163,16 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="411">
@@ -9183,16 +9183,16 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="412">
@@ -9203,16 +9203,16 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -9243,16 +9243,16 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -9288,11 +9288,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D417" t="n">
@@ -9328,11 +9328,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -9343,16 +9343,16 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D420" t="n">
@@ -9383,16 +9383,16 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422">
@@ -9403,16 +9403,16 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="423">
@@ -9428,11 +9428,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="424">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -9468,11 +9468,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="426">
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -9528,11 +9528,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="430">
@@ -9563,16 +9563,16 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="431">
@@ -9583,16 +9583,16 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="432">
@@ -9603,16 +9603,16 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="433">
@@ -9623,16 +9623,16 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D434" t="n">
@@ -9668,47 +9668,47 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D437" t="n">
@@ -9718,41 +9718,41 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="440">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442">
@@ -9803,12 +9803,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D442" t="n">
@@ -9823,12 +9823,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D443" t="n">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="446">
@@ -9888,11 +9888,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -9923,12 +9923,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D448" t="n">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -9963,16 +9963,16 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -9988,11 +9988,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="452">
@@ -10008,11 +10008,11 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -10023,16 +10023,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -10043,16 +10043,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -10063,16 +10063,16 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="456">
@@ -10083,16 +10083,16 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="457">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="458">
@@ -10128,11 +10128,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="459">
@@ -10148,11 +10148,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
@@ -10168,11 +10168,11 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="461">
@@ -10188,11 +10188,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="462">
@@ -10203,16 +10203,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="463">
@@ -10223,16 +10223,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="464">
@@ -10243,16 +10243,16 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="465">
@@ -10263,16 +10263,16 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="468">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="469">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10352,7 +10352,7 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="470">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="471">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -10392,7 +10392,7 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="472">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D472" t="n">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D473" t="n">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D474" t="n">
@@ -10463,16 +10463,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -10488,11 +10488,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="477">
@@ -10508,11 +10508,11 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -10528,11 +10528,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -10583,16 +10583,16 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D482" t="n">
@@ -10623,16 +10623,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="484">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="485">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D485" t="n">
@@ -10683,12 +10683,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -10703,16 +10703,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="488">
@@ -10728,11 +10728,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="489">
@@ -10748,11 +10748,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="490">
@@ -10768,11 +10768,11 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -10788,111 +10788,111 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -10928,11 +10928,11 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="499">
@@ -10948,11 +10948,11 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="500">
@@ -10968,11 +10968,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501">
@@ -10988,11 +10988,11 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>116</v>
+        <v>4</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="504">
@@ -11043,16 +11043,16 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="505">
@@ -11063,16 +11063,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="506">
@@ -11083,16 +11083,16 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
     </row>
     <row r="507">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="508">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D508" t="n">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="510">
@@ -11163,16 +11163,16 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511">
@@ -11183,16 +11183,16 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="513">
@@ -11223,16 +11223,16 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -11243,16 +11243,16 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="517">
@@ -11303,16 +11303,16 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="519">
@@ -11343,16 +11343,16 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="520">
@@ -11363,16 +11363,16 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="521">
@@ -11383,16 +11383,16 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="522">
@@ -11408,11 +11408,11 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="525">
@@ -11468,11 +11468,11 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="527">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="530">
@@ -11563,16 +11563,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="531">
@@ -11583,16 +11583,16 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="532">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D532" t="n">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="534">
@@ -11648,11 +11648,11 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="535">
@@ -11668,11 +11668,11 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="536">
@@ -11683,16 +11683,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="537">
@@ -11703,16 +11703,16 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="538">
@@ -11723,16 +11723,16 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="539">
@@ -11743,16 +11743,16 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="540">
@@ -11763,16 +11763,16 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="541">
@@ -11788,11 +11788,11 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="542">
@@ -11803,16 +11803,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -11823,16 +11823,16 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D544" t="n">
@@ -11863,16 +11863,16 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="546">
@@ -11883,16 +11883,16 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="547">
@@ -11908,11 +11908,11 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="548">
@@ -11928,11 +11928,11 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="549">
@@ -11943,16 +11943,16 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -11963,16 +11963,16 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -11983,16 +11983,16 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="552">
@@ -12003,16 +12003,16 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -12023,16 +12023,16 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="554">
@@ -12048,11 +12048,11 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="555">
@@ -12068,11 +12068,11 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556">
@@ -12088,11 +12088,11 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="557">
@@ -12108,11 +12108,11 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="558">
@@ -12123,16 +12123,16 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -12152,7 +12152,7 @@
         </is>
       </c>
       <c r="D559" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="560">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -12172,7 +12172,7 @@
         </is>
       </c>
       <c r="D560" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="561">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -12212,7 +12212,7 @@
         </is>
       </c>
       <c r="D562" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="563">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="D563" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564">
@@ -12243,12 +12243,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D564" t="n">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D565" t="n">
@@ -12283,16 +12283,16 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567">
@@ -12303,16 +12303,16 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="568">
@@ -12328,11 +12328,11 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="569">
@@ -12348,11 +12348,11 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570">
@@ -12368,11 +12368,11 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="571">
@@ -12388,10 +12388,110 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D571" t="n">
+      <c r="D576" t="n">
         <v>12</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -513,10 +513,10 @@
         <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2" t="n">
-        <v>5666</v>
+        <v>5665</v>
       </c>
     </row>
     <row r="3">
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="L12" t="n">
-        <v>1091</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="13">
@@ -953,10 +953,10 @@
         <v>1359</v>
       </c>
       <c r="K13" t="n">
-        <v>963</v>
+        <v>986</v>
       </c>
       <c r="L13" t="n">
-        <v>13479</v>
+        <v>13502</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D576"/>
+  <dimension ref="A1:D580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
     <row r="172">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="201">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="207">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="208">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="217">
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="237">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="259">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="261">
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="278">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="283">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="284">
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="307">
@@ -8018,17 +8018,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -8103,16 +8103,16 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -8128,11 +8128,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="359">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -8168,11 +8168,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
@@ -8188,11 +8188,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -8208,11 +8208,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="363">
@@ -8223,16 +8223,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
@@ -8248,11 +8248,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368">
@@ -8323,16 +8323,16 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="369">
@@ -8343,12 +8343,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -8408,31 +8408,31 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="376">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -8528,11 +8528,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -8548,11 +8548,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -8568,11 +8568,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -8588,11 +8588,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -8603,16 +8603,16 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387">
@@ -8708,11 +8708,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="390">
@@ -8763,16 +8763,16 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="391">
@@ -8783,16 +8783,16 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="392">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="393">
@@ -8828,11 +8828,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -8863,16 +8863,16 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -8903,16 +8903,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="399">
@@ -8948,11 +8948,11 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400">
@@ -8968,11 +8968,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="401">
@@ -8988,11 +8988,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="402">
@@ -9008,11 +9008,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="403">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="404">
@@ -9043,16 +9043,16 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="405">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="412">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="414">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="415">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -9272,7 +9272,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="416">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -9303,12 +9303,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D417" t="n">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D420" t="n">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423">
@@ -9423,16 +9423,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="426">
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -9528,11 +9528,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="429">
@@ -9548,11 +9548,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="433">
@@ -9623,16 +9623,16 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="434">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="435">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -9703,16 +9703,16 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="439">
@@ -9748,27 +9748,27 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D440" t="n">
@@ -9778,37 +9778,37 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D442" t="n">
@@ -9818,21 +9818,21 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="444">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
@@ -9868,11 +9868,11 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D446" t="n">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D447" t="n">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -9943,16 +9943,16 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="450">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -9983,16 +9983,16 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -10023,12 +10023,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D453" t="n">
@@ -10043,16 +10043,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -10068,11 +10068,11 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -10103,16 +10103,16 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -10123,16 +10123,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="460">
@@ -10163,16 +10163,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="461">
@@ -10188,11 +10188,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="462">
@@ -10208,11 +10208,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="463">
@@ -10228,11 +10228,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="466">
@@ -10283,16 +10283,16 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="469">
@@ -10343,16 +10343,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="470">
@@ -10368,11 +10368,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="472">
@@ -10403,16 +10403,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -10423,16 +10423,16 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -10443,16 +10443,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="476">
@@ -10483,16 +10483,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D477" t="n">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D478" t="n">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="481">
@@ -10588,11 +10588,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
@@ -10628,11 +10628,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="486">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="487">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -10712,7 +10712,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="488">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -10732,7 +10732,7 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
@@ -10888,91 +10888,91 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="502">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="503">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="506">
@@ -11088,11 +11088,11 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>116</v>
+        <v>13</v>
       </c>
     </row>
     <row r="507">
@@ -11103,16 +11103,16 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="508">
@@ -11123,16 +11123,16 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="509">
@@ -11143,16 +11143,16 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -11163,16 +11163,16 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="511">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="512">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513">
@@ -11228,11 +11228,11 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="514">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515">
@@ -11263,16 +11263,16 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="516">
@@ -11283,16 +11283,16 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="517">
@@ -11303,16 +11303,16 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="518">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="521">
@@ -11388,11 +11388,11 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="523">
@@ -11423,16 +11423,16 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="524">
@@ -11443,16 +11443,16 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="525">
@@ -11463,16 +11463,16 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="526">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="527">
@@ -11508,11 +11508,11 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -11528,11 +11528,11 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="529">
@@ -11548,11 +11548,11 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530">
@@ -11568,11 +11568,11 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="531">
@@ -11588,11 +11588,11 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
     </row>
     <row r="532">
@@ -11603,16 +11603,16 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="533">
@@ -11623,16 +11623,16 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="534">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="536">
@@ -11688,11 +11688,11 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="537">
@@ -11708,11 +11708,11 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538">
@@ -11728,11 +11728,11 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="539">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D539" t="n">
@@ -11768,11 +11768,11 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541">
@@ -11783,16 +11783,16 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="542">
@@ -11803,16 +11803,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="543">
@@ -11823,16 +11823,16 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="545">
@@ -11868,11 +11868,11 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="546">
@@ -11888,11 +11888,11 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="547">
@@ -11903,16 +11903,16 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="548">
@@ -11923,16 +11923,16 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
@@ -11943,16 +11943,16 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="550">
@@ -11963,16 +11963,16 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="551">
@@ -11988,11 +11988,11 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="552">
@@ -12008,11 +12008,11 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="553">
@@ -12028,11 +12028,11 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
@@ -12043,16 +12043,16 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -12063,16 +12063,16 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="556">
@@ -12083,16 +12083,16 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -12103,16 +12103,16 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="558">
@@ -12128,11 +12128,11 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="559">
@@ -12148,11 +12148,11 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="560">
@@ -12168,11 +12168,11 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="561">
@@ -12188,11 +12188,11 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="562">
@@ -12208,11 +12208,11 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="563">
@@ -12223,16 +12223,16 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="564">
@@ -12243,16 +12243,16 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D564" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="565">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D565" t="n">
@@ -12283,16 +12283,16 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="567">
@@ -12308,11 +12308,11 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="568">
@@ -12323,16 +12323,16 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="569">
@@ -12343,16 +12343,16 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570">
@@ -12363,12 +12363,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D570" t="n">
@@ -12383,16 +12383,16 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="572">
@@ -12408,11 +12408,11 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="573">
@@ -12428,11 +12428,11 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D573" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -12448,11 +12448,11 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D574" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="575">
@@ -12468,11 +12468,11 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D575" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="576">
@@ -12488,10 +12488,90 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D576" t="n">
+      <c r="D580" t="n">
         <v>12</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -630,10 +630,10 @@
         <v>113</v>
       </c>
       <c r="J5" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L5" t="n">
         <v>1398</v>
@@ -652,7 +652,7 @@
         <v>239</v>
       </c>
       <c r="D6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" t="n">
         <v>32</v>
@@ -673,10 +673,10 @@
         <v>104</v>
       </c>
       <c r="K6" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L6" t="n">
-        <v>1044</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="7">
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C7" t="n">
         <v>417</v>
       </c>
       <c r="D7" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E7" t="n">
         <v>49</v>
@@ -710,13 +710,13 @@
         <v>172</v>
       </c>
       <c r="J7" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K7" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="L7" t="n">
-        <v>1791</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="8">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8" t="n">
         <v>41</v>
@@ -769,7 +769,7 @@
         <v>115</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" t="n">
         <v>28</v>
@@ -796,7 +796,7 @@
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="L12" t="n">
-        <v>1115</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="13">
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D580"/>
+  <dimension ref="A1:D579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="89">
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="126">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="135">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="144">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="172">
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="193">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="207">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="209">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="210">
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="217">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="219">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="245">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="252">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="260">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="271">
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="285">
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="286">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="306">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="312">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364">
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="369">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8488,11 +8488,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -8508,11 +8508,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -8528,11 +8528,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -8568,11 +8568,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="381">
@@ -8588,11 +8588,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="382">
@@ -8608,11 +8608,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="391">
@@ -8783,16 +8783,16 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="392">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
@@ -8828,11 +8828,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="394">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D394" t="n">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D395" t="n">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -8903,16 +8903,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="398">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399">
@@ -8948,11 +8948,11 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="400">
@@ -8968,11 +8968,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="401">
@@ -8988,11 +8988,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="402">
@@ -9008,11 +9008,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="403">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="404">
@@ -9048,11 +9048,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="405">
@@ -9068,11 +9068,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="407">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="411">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="412">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="413">
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -9288,11 +9288,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D417" t="n">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D421" t="n">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D423" t="n">
@@ -9448,11 +9448,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="425">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="426">
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="428">
@@ -9528,11 +9528,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -9548,11 +9548,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="432">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="433">
@@ -9628,11 +9628,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="434">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="435">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -9688,11 +9688,11 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -9703,16 +9703,16 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="438">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="439">
@@ -9748,11 +9748,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442">
@@ -9808,31 +9808,31 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444">
@@ -9843,12 +9843,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D444" t="n">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -9888,11 +9888,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -9908,11 +9908,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -9928,11 +9928,11 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="449">
@@ -9943,16 +9943,16 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -9988,11 +9988,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -10028,11 +10028,11 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -10043,16 +10043,16 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="455">
@@ -10068,11 +10068,11 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D456" t="n">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D457" t="n">
@@ -10128,11 +10128,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="459">
@@ -10148,11 +10148,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="460">
@@ -10163,16 +10163,16 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="461">
@@ -10188,11 +10188,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="462">
@@ -10208,11 +10208,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
@@ -10228,11 +10228,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="467">
@@ -10308,11 +10308,11 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="468">
@@ -10328,11 +10328,11 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="469">
@@ -10343,16 +10343,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="470">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D470" t="n">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D471" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D472" t="n">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="474">
@@ -10443,16 +10443,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="476">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D476" t="n">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D477" t="n">
@@ -10528,11 +10528,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="480">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D482" t="n">
@@ -10628,11 +10628,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="484">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -10668,11 +10668,11 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="486">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="487">
@@ -10703,16 +10703,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -10728,11 +10728,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D489" t="n">
@@ -10768,11 +10768,11 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="491">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D494" t="n">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -10908,11 +10908,11 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="498">
@@ -10928,11 +10928,11 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="499">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D499" t="n">
@@ -10958,21 +10958,21 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="502">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="503">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="505">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="506">
@@ -11088,11 +11088,11 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="507">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="508">
@@ -11128,11 +11128,11 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="509">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="510">
@@ -11163,16 +11163,16 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>116</v>
+        <v>4</v>
       </c>
     </row>
     <row r="511">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="513">
@@ -11228,11 +11228,11 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="515">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D515" t="n">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="518">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="521">
@@ -11388,11 +11388,11 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="522">
@@ -11408,11 +11408,11 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="525">
@@ -11463,16 +11463,16 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="526">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
@@ -11508,11 +11508,11 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="528">
@@ -11528,11 +11528,11 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529">
@@ -11548,11 +11548,11 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="530">
@@ -11568,11 +11568,11 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="531">
@@ -11588,11 +11588,11 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="532">
@@ -11608,11 +11608,11 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="533">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="534">
@@ -11648,11 +11648,11 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
     </row>
     <row r="536">
@@ -11688,11 +11688,11 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="537">
@@ -11708,11 +11708,11 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="538">
@@ -11728,11 +11728,11 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="539">
@@ -11748,11 +11748,11 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540">
@@ -11768,11 +11768,11 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="541">
@@ -11788,11 +11788,11 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="542">
@@ -11808,11 +11808,11 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="543">
@@ -11828,11 +11828,11 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="545">
@@ -11868,11 +11868,11 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="546">
@@ -11888,11 +11888,11 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D547" t="n">
@@ -11928,11 +11928,11 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="549">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="550">
@@ -11963,16 +11963,16 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="551">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D551" t="n">
@@ -12008,11 +12008,11 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D553" t="n">
@@ -12048,11 +12048,11 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="555">
@@ -12068,11 +12068,11 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556">
@@ -12088,11 +12088,11 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="557">
@@ -12103,16 +12103,16 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="558">
@@ -12128,11 +12128,11 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -12148,11 +12148,11 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="560">
@@ -12168,11 +12168,11 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="561">
@@ -12188,11 +12188,11 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="562">
@@ -12208,11 +12208,11 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="563">
@@ -12228,11 +12228,11 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="564">
@@ -12248,11 +12248,11 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D564" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="565">
@@ -12268,11 +12268,11 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D565" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="566">
@@ -12283,16 +12283,16 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567">
@@ -12308,11 +12308,11 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568">
@@ -12328,11 +12328,11 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="569">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D569" t="n">
@@ -12368,11 +12368,11 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="571">
@@ -12383,16 +12383,16 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="572">
@@ -12408,11 +12408,11 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="573">
@@ -12428,11 +12428,11 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D573" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="574">
@@ -12448,11 +12448,11 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D574" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="575">
@@ -12468,11 +12468,11 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D575" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="576">
@@ -12488,11 +12488,11 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D576" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="577">
@@ -12508,11 +12508,11 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D577" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="578">
@@ -12528,11 +12528,11 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D578" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="579">
@@ -12548,30 +12548,10 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D579" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C580" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
-      <c r="D580" t="n">
         <v>12</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -489,7 +489,7 @@
         <v>3059</v>
       </c>
       <c r="C2" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D2" t="n">
         <v>358</v>
@@ -513,10 +513,10 @@
         <v>480</v>
       </c>
       <c r="K2" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L2" t="n">
-        <v>5640</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="3">
@@ -569,7 +569,7 @@
         <v>345</v>
       </c>
       <c r="C4" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D4" t="n">
         <v>126</v>
@@ -596,7 +596,7 @@
         <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="5">
@@ -707,7 +707,7 @@
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J7" t="n">
         <v>202</v>
@@ -716,7 +716,7 @@
         <v>193</v>
       </c>
       <c r="L7" t="n">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="8">
@@ -889,7 +889,7 @@
         <v>97</v>
       </c>
       <c r="C12" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D12" t="n">
         <v>82</v>
@@ -913,10 +913,10 @@
         <v>208</v>
       </c>
       <c r="K12" t="n">
-        <v>359</v>
+        <v>314</v>
       </c>
       <c r="L12" t="n">
-        <v>1277</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="13">
@@ -929,7 +929,7 @@
         <v>5357</v>
       </c>
       <c r="C13" t="n">
-        <v>2693</v>
+        <v>2697</v>
       </c>
       <c r="D13" t="n">
         <v>1224</v>
@@ -947,16 +947,16 @@
         <v>128</v>
       </c>
       <c r="I13" t="n">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="J13" t="n">
         <v>1362</v>
       </c>
       <c r="K13" t="n">
-        <v>1094</v>
+        <v>1050</v>
       </c>
       <c r="L13" t="n">
-        <v>13628</v>
+        <v>13587</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D596"/>
+  <dimension ref="A1:D597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="166">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="172">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="203">
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="262">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="295">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="318">
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -8118,17 +8118,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D362" t="n">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D363" t="n">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -8408,11 +8408,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="377">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -8568,31 +8568,31 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
@@ -8608,11 +8608,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -8628,11 +8628,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -8648,11 +8648,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="385">
@@ -8663,16 +8663,16 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="386">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -8708,11 +8708,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="392">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="393">
@@ -8828,11 +8828,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="394">
@@ -8843,16 +8843,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="396">
@@ -8888,11 +8888,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="397">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -8948,11 +8948,11 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
@@ -8968,11 +8968,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401">
@@ -8988,11 +8988,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="402">
@@ -9003,16 +9003,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="403">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="404">
@@ -9048,11 +9048,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D405" t="n">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D406" t="n">
@@ -9108,11 +9108,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
@@ -9123,16 +9123,16 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="412">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="413">
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="415">
@@ -9268,11 +9268,11 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="416">
@@ -9288,11 +9288,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="418">
@@ -9328,11 +9328,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="423">
@@ -9428,11 +9428,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="424">
@@ -9448,11 +9448,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="425">
@@ -9468,11 +9468,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="426">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D432" t="n">
@@ -9628,11 +9628,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -9668,11 +9668,11 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="437">
@@ -9708,11 +9708,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="438">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -9748,11 +9748,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="440">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="442">
@@ -9808,11 +9808,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443">
@@ -9828,11 +9828,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="444">
@@ -9848,11 +9848,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="445">
@@ -9868,11 +9868,11 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="447">
@@ -9908,11 +9908,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -9948,11 +9948,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="450">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -9988,11 +9988,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -10008,11 +10008,11 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D453" t="n">
@@ -10048,31 +10048,31 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -10128,11 +10128,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="460">
@@ -10168,11 +10168,11 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461">
@@ -10188,11 +10188,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462">
@@ -10208,11 +10208,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -10223,16 +10223,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="464">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D466" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D467" t="n">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -10348,11 +10348,11 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="470">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D470" t="n">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D471" t="n">
@@ -10408,11 +10408,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="474">
@@ -10443,16 +10443,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="476">
@@ -10488,11 +10488,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="477">
@@ -10508,11 +10508,11 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -10528,11 +10528,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="479">
@@ -10548,11 +10548,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="480">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="481">
@@ -10588,11 +10588,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="482">
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="483">
@@ -10623,16 +10623,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="484">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D485" t="n">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -10708,11 +10708,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="489">
@@ -10748,11 +10748,11 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="490">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D491" t="n">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="493">
@@ -10823,16 +10823,16 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="495">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D495" t="n">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -10908,11 +10908,11 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -10948,11 +10948,11 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -10968,11 +10968,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="502">
@@ -11008,11 +11008,11 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D503" t="n">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -11063,16 +11063,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="506">
@@ -11088,11 +11088,11 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="507">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="508">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D508" t="n">
@@ -11148,11 +11148,11 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D510" t="n">
@@ -11188,11 +11188,11 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="512">
@@ -11208,11 +11208,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="513">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -11238,21 +11238,21 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="515">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D515" t="n">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="518">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="520">
@@ -11368,11 +11368,11 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="521">
@@ -11388,11 +11388,11 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
@@ -11408,11 +11408,11 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="525">
@@ -11468,11 +11468,11 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="526">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
     </row>
     <row r="528">
@@ -11528,11 +11528,11 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="529">
@@ -11548,11 +11548,11 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530">
@@ -11568,11 +11568,11 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="531">
@@ -11588,11 +11588,11 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532">
@@ -11608,7 +11608,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D532" t="n">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="534">
@@ -11648,11 +11648,11 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="536">
@@ -11688,11 +11688,11 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="537">
@@ -11708,11 +11708,11 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="538">
@@ -11728,11 +11728,11 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -11748,11 +11748,11 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="540">
@@ -11768,11 +11768,11 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="541">
@@ -11788,11 +11788,11 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="542">
@@ -11803,16 +11803,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
     </row>
     <row r="543">
@@ -11828,11 +11828,11 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="544">
@@ -11848,11 +11848,11 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -11868,11 +11868,11 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="546">
@@ -11888,11 +11888,11 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
@@ -11908,11 +11908,11 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="548">
@@ -11928,11 +11928,11 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="549">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="550">
@@ -11968,11 +11968,11 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="551">
@@ -11988,11 +11988,11 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="552">
@@ -12003,16 +12003,16 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="553">
@@ -12028,11 +12028,11 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="554">
@@ -12048,11 +12048,11 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -12068,11 +12068,11 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="556">
@@ -12088,11 +12088,11 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="557">
@@ -12108,11 +12108,11 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="558">
@@ -12128,11 +12128,11 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="559">
@@ -12148,11 +12148,11 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="560">
@@ -12168,11 +12168,11 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="561">
@@ -12183,16 +12183,16 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="562">
@@ -12208,11 +12208,11 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="563">
@@ -12228,11 +12228,11 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D564" t="n">
@@ -12268,11 +12268,11 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D565" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="566">
@@ -12288,11 +12288,11 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="567">
@@ -12303,16 +12303,16 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="568">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D568" t="n">
@@ -12348,11 +12348,11 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="570">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D570" t="n">
@@ -12388,11 +12388,11 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="572">
@@ -12408,11 +12408,11 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="573">
@@ -12428,11 +12428,11 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D573" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -12443,16 +12443,16 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D574" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="575">
@@ -12468,11 +12468,11 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D575" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="576">
@@ -12488,11 +12488,11 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D576" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="577">
@@ -12508,11 +12508,11 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D577" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="578">
@@ -12528,11 +12528,11 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D578" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="579">
@@ -12548,11 +12548,11 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D579" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="580">
@@ -12568,11 +12568,11 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D580" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="581">
@@ -12588,11 +12588,11 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D581" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="582">
@@ -12608,11 +12608,11 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D582" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="583">
@@ -12623,16 +12623,16 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D583" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="584">
@@ -12648,11 +12648,11 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D584" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585">
@@ -12668,11 +12668,11 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D585" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="586">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D586" t="n">
@@ -12708,11 +12708,11 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D587" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="588">
@@ -12723,16 +12723,16 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D588" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="589">
@@ -12748,11 +12748,11 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D589" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="590">
@@ -12768,11 +12768,11 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D590" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="591">
@@ -12788,11 +12788,11 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D591" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="592">
@@ -12808,11 +12808,11 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D592" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="593">
@@ -12828,11 +12828,11 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D593" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="594">
@@ -12848,11 +12848,11 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D594" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="595">
@@ -12868,11 +12868,11 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D595" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="596">
@@ -12888,10 +12888,30 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D596" t="n">
+      <c r="D597" t="n">
         <v>12</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -486,37 +486,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3059</v>
+        <v>3037</v>
       </c>
       <c r="C2" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D2" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F2" t="n">
+        <v>228</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H2" t="n">
+        <v>53</v>
+      </c>
+      <c r="I2" t="n">
+        <v>306</v>
+      </c>
+      <c r="J2" t="n">
+        <v>473</v>
+      </c>
+      <c r="K2" t="n">
         <v>230</v>
       </c>
-      <c r="G2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H2" t="n">
-        <v>55</v>
-      </c>
-      <c r="I2" t="n">
-        <v>314</v>
-      </c>
-      <c r="J2" t="n">
-        <v>480</v>
-      </c>
-      <c r="K2" t="n">
-        <v>240</v>
-      </c>
       <c r="L2" t="n">
-        <v>5641</v>
+        <v>5588</v>
       </c>
     </row>
     <row r="3">
@@ -529,13 +529,13 @@
         <v>281</v>
       </c>
       <c r="C3" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
         <v>17</v>
@@ -544,19 +544,19 @@
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
         <v>53</v>
       </c>
       <c r="J3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>675</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C4" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
@@ -584,19 +584,19 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J4" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K4" t="n">
         <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>941</v>
+        <v>927</v>
       </c>
     </row>
     <row r="5">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="C5" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D5" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
         <v>30</v>
@@ -627,16 +627,16 @@
         <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J5" t="n">
         <v>138</v>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="L5" t="n">
-        <v>1387</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="6">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C6" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D6" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
         <v>8</v>
@@ -667,16 +667,16 @@
         <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J6" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K6" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="L6" t="n">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="7">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C7" t="n">
         <v>414</v>
       </c>
       <c r="D7" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
         <v>41</v>
@@ -704,19 +704,19 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J7" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K7" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="L7" t="n">
-        <v>1797</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="8">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
         <v>13</v>
@@ -753,10 +753,10 @@
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
         <v>5</v>
@@ -787,16 +787,16 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
@@ -904,19 +904,19 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="J12" t="n">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>346</v>
+        <v>475</v>
       </c>
       <c r="L12" t="n">
-        <v>1266</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="13">
@@ -926,37 +926,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5357</v>
+        <v>5292</v>
       </c>
       <c r="C13" t="n">
-        <v>2697</v>
+        <v>2661</v>
       </c>
       <c r="D13" t="n">
-        <v>1224</v>
+        <v>1200</v>
       </c>
       <c r="E13" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="F13" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H13" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I13" t="n">
-        <v>988</v>
+        <v>967</v>
       </c>
       <c r="J13" t="n">
-        <v>1362</v>
+        <v>1338</v>
       </c>
       <c r="K13" t="n">
-        <v>1080</v>
+        <v>1251</v>
       </c>
       <c r="L13" t="n">
-        <v>13617</v>
+        <v>13604</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D602"/>
+  <dimension ref="A1:D585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1083,16 +1083,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1108,11 +1108,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1128,11 +1128,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1188,11 +1188,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1268,11 +1268,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1283,16 +1283,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1328,11 +1328,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1348,11 +1348,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1368,11 +1368,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1408,11 +1408,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46">
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>91</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="53">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="55">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>456</v>
+        <v>449</v>
       </c>
     </row>
     <row r="59">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="60">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2963</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="62">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="63">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72">
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82">
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="83">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="87">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="92">
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="93">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="100">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="101">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>441</v>
+        <v>434</v>
       </c>
     </row>
     <row r="102">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="112">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="118">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="119">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120">
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="122">
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="124">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126">
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="128">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="129">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="130">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="131">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="138">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142">
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="146">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="147">
@@ -3903,16 +3903,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -3928,11 +3928,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -3968,11 +3968,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -3983,16 +3983,16 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -4048,11 +4048,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
@@ -4063,16 +4063,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -4163,16 +4163,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4188,11 +4188,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -4223,16 +4223,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -4288,31 +4288,31 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="168">
@@ -4328,11 +4328,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
@@ -4388,11 +4388,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172">
@@ -4408,11 +4408,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173">
@@ -4428,11 +4428,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>9</v>
+        <v>235</v>
       </c>
     </row>
     <row r="174">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>217</v>
+        <v>9</v>
       </c>
     </row>
     <row r="175">
@@ -4463,16 +4463,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
     </row>
     <row r="176">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4508,11 +4508,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178">
@@ -4528,11 +4528,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -4548,11 +4548,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180">
@@ -4568,11 +4568,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
     </row>
     <row r="184">
@@ -4648,11 +4648,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
     </row>
     <row r="185">
@@ -4663,16 +4663,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>93</v>
+        <v>26</v>
       </c>
     </row>
     <row r="186">
@@ -4688,11 +4688,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -4768,11 +4768,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191">
@@ -4788,11 +4788,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192">
@@ -4808,11 +4808,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="194">
@@ -4843,16 +4843,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="195">
@@ -4868,11 +4868,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196">
@@ -4888,11 +4888,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -4928,11 +4928,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199">
@@ -4948,11 +4948,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200">
@@ -4968,11 +4968,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201">
@@ -4988,11 +4988,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="202">
@@ -5003,16 +5003,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>15</v>
+        <v>165</v>
       </c>
     </row>
     <row r="203">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>167</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="205">
@@ -5068,11 +5068,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -5088,11 +5088,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="207">
@@ -5108,11 +5108,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208">
@@ -5128,11 +5128,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="209">
@@ -5148,11 +5148,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="210">
@@ -5168,11 +5168,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="211">
@@ -5188,11 +5188,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
     </row>
     <row r="212">
@@ -5203,16 +5203,16 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="213">
@@ -5228,11 +5228,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -5248,11 +5248,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="215">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217">
@@ -5308,11 +5308,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218">
@@ -5328,11 +5328,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="219">
@@ -5348,11 +5348,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="220">
@@ -5368,11 +5368,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="221">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>16</v>
+        <v>87</v>
       </c>
     </row>
     <row r="222">
@@ -5403,16 +5403,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>91</v>
+        <v>10</v>
       </c>
     </row>
     <row r="223">
@@ -5428,11 +5428,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -5468,11 +5468,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -5488,11 +5488,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="227">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228">
@@ -5528,11 +5528,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="229">
@@ -5543,16 +5543,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="230">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="231">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -5608,11 +5608,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="234">
@@ -5648,11 +5648,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235">
@@ -5668,11 +5668,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="237">
@@ -5703,16 +5703,16 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="238">
@@ -5723,16 +5723,16 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="240">
@@ -5768,11 +5768,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -5788,11 +5788,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="242">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -5828,11 +5828,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="244">
@@ -5848,11 +5848,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="245">
@@ -5868,11 +5868,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="246">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>35</v>
+        <v>83</v>
       </c>
     </row>
     <row r="247">
@@ -5903,16 +5903,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248">
@@ -5923,16 +5923,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249">
@@ -5948,11 +5948,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="252">
@@ -6003,16 +6003,16 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="253">
@@ -6023,16 +6023,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="254">
@@ -6048,11 +6048,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6068,11 +6068,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256">
@@ -6088,11 +6088,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="257">
@@ -6108,11 +6108,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="258">
@@ -6128,11 +6128,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="259">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -6168,22 +6168,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6192,27 +6192,27 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -6243,16 +6243,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="267">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6323,16 +6323,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="269">
@@ -6343,16 +6343,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="271">
@@ -6383,16 +6383,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -6423,16 +6423,16 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274">
@@ -6443,16 +6443,16 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6488,11 +6488,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277">
@@ -6503,16 +6503,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="278">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -6543,16 +6543,16 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="280">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -6583,16 +6583,16 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="282">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="283">
@@ -6628,11 +6628,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="284">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="285">
@@ -6668,11 +6668,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="286">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -6703,16 +6703,16 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -6723,16 +6723,16 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -6743,16 +6743,16 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -6763,16 +6763,16 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="292">
@@ -6808,11 +6808,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293">
@@ -6823,16 +6823,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6872,7 +6872,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -6923,16 +6923,16 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -6963,16 +6963,16 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="301">
@@ -6983,16 +6983,16 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D302" t="n">
@@ -7023,16 +7023,16 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="304">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -7088,11 +7088,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="307">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="308">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="309">
@@ -7143,16 +7143,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -7203,16 +7203,16 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="313">
@@ -7223,16 +7223,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="314">
@@ -7243,16 +7243,16 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -7263,16 +7263,16 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -7283,16 +7283,16 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="317">
@@ -7303,16 +7303,16 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -7348,111 +7348,111 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>3</v>
+        <v>266</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="325">
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>270</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>5</v>
+        <v>151</v>
       </c>
     </row>
     <row r="327">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="328">
@@ -7528,11 +7528,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="329">
@@ -7548,11 +7548,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="330">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="331">
@@ -7583,16 +7583,16 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -7603,16 +7603,16 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -7623,16 +7623,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -7643,16 +7643,16 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -7708,11 +7708,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="339">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="340">
@@ -7763,16 +7763,16 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D345" t="n">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -7903,32 +7903,32 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -7938,57 +7938,57 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -7998,17 +7998,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -8023,16 +8023,16 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354">
@@ -8043,12 +8043,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -8083,16 +8083,16 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -8118,12 +8118,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8138,37 +8138,37 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D360" t="n">
@@ -8178,17 +8178,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -8198,17 +8198,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D362" t="n">
@@ -8218,12 +8218,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="364">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="365">
@@ -8263,16 +8263,16 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -8303,16 +8303,16 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="368">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -8343,16 +8343,16 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="370">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -8503,16 +8503,16 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -8543,12 +8543,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8592,18 +8592,18 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8612,18 +8612,18 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -8632,43 +8632,43 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -8678,21 +8678,21 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -8723,16 +8723,16 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="390">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="391">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="392">
@@ -8803,16 +8803,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -8843,16 +8843,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="395">
@@ -8863,16 +8863,16 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -8883,16 +8883,16 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="397">
@@ -8903,16 +8903,16 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="398">
@@ -8923,16 +8923,16 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="399">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="400">
@@ -8963,16 +8963,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="402">
@@ -9003,16 +9003,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="403">
@@ -9023,16 +9023,16 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
@@ -9043,12 +9043,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
@@ -9103,16 +9103,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="408">
@@ -9123,16 +9123,16 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="409">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="410">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="411">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="412">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -9212,7 +9212,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="413">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="414">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="418">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="419">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="420">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="421">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="422">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -9412,7 +9412,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="423">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D425" t="n">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
@@ -9503,16 +9503,16 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="428">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="432">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="433">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="435">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -9703,16 +9703,16 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -9723,7 +9723,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="439">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="440">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="441">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="442">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="443">
@@ -9823,16 +9823,16 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -9943,16 +9943,16 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -9978,177 +9978,177 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D459" t="n">
@@ -10158,12 +10158,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="462">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10223,16 +10223,16 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
@@ -10243,16 +10243,16 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
@@ -10263,16 +10263,16 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="466">
@@ -10283,16 +10283,16 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="469">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D469" t="n">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472">
@@ -10403,16 +10403,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="473">
@@ -10423,16 +10423,16 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="474">
@@ -10443,16 +10443,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="475">
@@ -10463,16 +10463,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="476">
@@ -10483,16 +10483,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="481">
@@ -10583,16 +10583,16 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="482">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D482" t="n">
@@ -10623,16 +10623,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485">
@@ -10663,16 +10663,16 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="486">
@@ -10683,16 +10683,16 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="487">
@@ -10703,16 +10703,16 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="493">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -10832,7 +10832,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="494">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D495" t="n">
@@ -10883,12 +10883,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="499">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D499" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D501" t="n">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="505">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="506">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -11092,223 +11092,223 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>3</v>
+        <v>115</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D517" t="n">
@@ -11318,41 +11318,41 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="520">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D520" t="n">
@@ -11383,16 +11383,16 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="523">
@@ -11423,16 +11423,16 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -11443,16 +11443,16 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="525">
@@ -11463,16 +11463,16 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="526">
@@ -11483,16 +11483,16 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="527">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="530">
@@ -11563,16 +11563,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="531">
@@ -11583,16 +11583,16 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="532">
@@ -11603,16 +11603,16 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>116</v>
+        <v>44</v>
       </c>
     </row>
     <row r="533">
@@ -11623,16 +11623,16 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536">
@@ -11683,16 +11683,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="537">
@@ -11703,16 +11703,16 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="538">
@@ -11723,16 +11723,16 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="539">
@@ -11743,16 +11743,16 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="540">
@@ -11763,16 +11763,16 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="541">
@@ -11783,16 +11783,16 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="542">
@@ -11803,16 +11803,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="543">
@@ -11823,16 +11823,16 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="545">
@@ -11863,16 +11863,16 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="546">
@@ -11883,16 +11883,16 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
@@ -11903,16 +11903,16 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="548">
@@ -11923,16 +11923,16 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
     </row>
     <row r="549">
@@ -11943,16 +11943,16 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="550">
@@ -11963,16 +11963,16 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="551">
@@ -11983,16 +11983,16 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="552">
@@ -12003,16 +12003,16 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553">
@@ -12023,16 +12023,16 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
@@ -12043,16 +12043,16 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="555">
@@ -12063,16 +12063,16 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="556">
@@ -12083,16 +12083,16 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="557">
@@ -12103,16 +12103,16 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="558">
@@ -12123,16 +12123,16 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D559" t="n">
@@ -12163,16 +12163,16 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="561">
@@ -12183,16 +12183,16 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="562">
@@ -12203,16 +12203,16 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="563">
@@ -12223,16 +12223,16 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="564">
@@ -12243,16 +12243,16 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D564" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="565">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D565" t="n">
@@ -12283,16 +12283,16 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="567">
@@ -12303,16 +12303,16 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568">
@@ -12323,16 +12323,16 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="569">
@@ -12343,16 +12343,16 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="570">
@@ -12363,16 +12363,16 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="571">
@@ -12383,16 +12383,16 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="572">
@@ -12403,16 +12403,16 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="573">
@@ -12423,16 +12423,16 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D573" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -12443,16 +12443,16 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D574" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="575">
@@ -12463,12 +12463,12 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D575" t="n">
@@ -12483,16 +12483,16 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D576" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="577">
@@ -12503,16 +12503,16 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D577" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="578">
@@ -12523,12 +12523,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D578" t="n">
@@ -12543,16 +12543,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D579" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="580">
@@ -12563,16 +12563,16 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D580" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="581">
@@ -12583,16 +12583,16 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D581" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="582">
@@ -12603,16 +12603,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D582" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="583">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D583" t="n">
@@ -12643,16 +12643,16 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D584" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="585">
@@ -12663,355 +12663,15 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D585" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C586" t="inlineStr">
-        <is>
-          <t>South Asian</t>
-        </is>
-      </c>
-      <c r="D586" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D587" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
-      <c r="D588" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
-      <c r="D589" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="D590" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>South Asian</t>
-        </is>
-      </c>
-      <c r="D591" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D592" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
-      <c r="D593" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>Black/African</t>
-        </is>
-      </c>
-      <c r="D594" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>Faceless</t>
-        </is>
-      </c>
-      <c r="D595" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>Hispanic/Latino</t>
-        </is>
-      </c>
-      <c r="D596" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>Middle Eastern/Arab</t>
-        </is>
-      </c>
-      <c r="D597" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>Mixed/Ambiguous</t>
-        </is>
-      </c>
-      <c r="D598" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="D599" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>South Asian</t>
-        </is>
-      </c>
-      <c r="D600" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D601" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
-      <c r="D602" t="n">
         <v>13</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -486,25 +486,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3037</v>
+        <v>3062</v>
       </c>
       <c r="C2" t="n">
-        <v>771</v>
+        <v>782</v>
       </c>
       <c r="D2" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E2" t="n">
         <v>101</v>
       </c>
       <c r="F2" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I2" t="n">
         <v>306</v>
@@ -513,10 +513,10 @@
         <v>473</v>
       </c>
       <c r="K2" t="n">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="L2" t="n">
-        <v>5588</v>
+        <v>5666</v>
       </c>
     </row>
     <row r="3">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" t="n">
         <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
         <v>17</v>
@@ -544,7 +544,7 @@
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
         <v>53</v>
@@ -553,10 +553,10 @@
         <v>61</v>
       </c>
       <c r="K3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3" t="n">
-        <v>669</v>
+        <v>678</v>
       </c>
     </row>
     <row r="4">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C4" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
@@ -593,10 +593,10 @@
         <v>91</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="L4" t="n">
-        <v>927</v>
+        <v>947</v>
       </c>
     </row>
     <row r="5">
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="C5" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="D5" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E5" t="n">
         <v>43</v>
@@ -633,10 +633,10 @@
         <v>138</v>
       </c>
       <c r="K5" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L5" t="n">
-        <v>1395</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="6">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C6" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D6" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
         <v>8</v>
@@ -673,10 +673,10 @@
         <v>102</v>
       </c>
       <c r="K6" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L6" t="n">
-        <v>1041</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="7">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C7" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D7" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
         <v>41</v>
@@ -713,10 +713,10 @@
         <v>200</v>
       </c>
       <c r="K7" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L7" t="n">
-        <v>1805</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="8">
@@ -729,13 +729,13 @@
         <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
         <v>17</v>
@@ -753,10 +753,10 @@
         <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9" t="n">
         <v>27</v>
@@ -793,10 +793,10 @@
         <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L9" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -809,10 +809,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="L10" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D12" t="n">
         <v>73</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>475</v>
+        <v>283</v>
       </c>
       <c r="L12" t="n">
-        <v>1317</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="13">
@@ -926,25 +926,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5292</v>
+        <v>5348</v>
       </c>
       <c r="C13" t="n">
-        <v>2661</v>
+        <v>2691</v>
       </c>
       <c r="D13" t="n">
-        <v>1200</v>
+        <v>1218</v>
       </c>
       <c r="E13" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F13" t="n">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="G13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H13" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I13" t="n">
         <v>967</v>
@@ -953,7 +953,7 @@
         <v>1338</v>
       </c>
       <c r="K13" t="n">
-        <v>1251</v>
+        <v>1132</v>
       </c>
       <c r="L13" t="n">
         <v>13604</v>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D585"/>
+  <dimension ref="A1:D592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,11 +1148,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1188,11 +1188,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1268,11 +1268,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1283,16 +1283,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1328,11 +1328,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1348,11 +1348,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1368,11 +1368,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1408,11 +1408,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>254</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>664</v>
+        <v>674</v>
       </c>
     </row>
     <row r="53">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="58">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>193</v>
+        <v>225</v>
       </c>
     </row>
     <row r="61">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2940</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="62">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72">
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="82">
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="83">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="92">
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="93">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="100">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="101">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>434</v>
+        <v>444</v>
       </c>
     </row>
     <row r="102">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="112">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113">
@@ -3272,7 +3272,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120">
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="121">
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="122">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126">
@@ -3492,7 +3492,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="129">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="131">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="138">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142">
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="145">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="168">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>235</v>
+        <v>200</v>
       </c>
     </row>
     <row r="174">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="184">
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="185">
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="193">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="195">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="201">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="202">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="203">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="210">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="211">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="212">
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="213">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="220">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="221">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="222">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -5588,11 +5588,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="232">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -5628,11 +5628,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -5648,11 +5648,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -5688,11 +5688,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -5703,16 +5703,16 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="238">
@@ -5728,11 +5728,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="239">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -5768,11 +5768,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="241">
@@ -5788,11 +5788,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="243">
@@ -5828,11 +5828,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -5848,11 +5848,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="245">
@@ -5868,11 +5868,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="246">
@@ -5888,11 +5888,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>83</v>
+        <v>32</v>
       </c>
     </row>
     <row r="247">
@@ -5903,16 +5903,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="248">
@@ -5928,11 +5928,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -6003,16 +6003,16 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="253">
@@ -6028,11 +6028,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="254">
@@ -6048,11 +6048,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="255">
@@ -6068,11 +6068,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -6088,11 +6088,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -6128,11 +6128,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="259">
@@ -6148,11 +6148,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="260">
@@ -6168,31 +6168,31 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="262">
@@ -6203,16 +6203,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267">
@@ -6303,16 +6303,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -6388,11 +6388,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="272">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -6503,16 +6503,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="279">
@@ -6548,11 +6548,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="281">
@@ -6588,11 +6588,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="282">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283">
@@ -6628,11 +6628,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="284">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="285">
@@ -6668,11 +6668,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="286">
@@ -6683,16 +6683,16 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="287">
@@ -6708,11 +6708,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
@@ -6768,11 +6768,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -6808,11 +6808,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="293">
@@ -6823,16 +6823,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294">
@@ -6848,11 +6848,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="295">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="298">
@@ -6923,16 +6923,16 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -6963,16 +6963,16 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="302">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -7028,11 +7028,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -7088,11 +7088,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="308">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D308" t="n">
@@ -7143,16 +7143,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="310">
@@ -7168,11 +7168,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -7223,16 +7223,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="314">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="315">
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="319">
@@ -7348,31 +7348,31 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>266</v>
+        <v>10</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>5</v>
+        <v>267</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323">
@@ -7428,11 +7428,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="324">
@@ -7448,11 +7448,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="326">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>151</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>46</v>
+        <v>151</v>
       </c>
     </row>
     <row r="328">
@@ -7528,11 +7528,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="329">
@@ -7548,11 +7548,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="330">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
     </row>
     <row r="331">
@@ -7588,11 +7588,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
     </row>
     <row r="332">
@@ -7608,11 +7608,11 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="337">
@@ -7708,11 +7708,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="338">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="340">
@@ -7768,11 +7768,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="341">
@@ -7783,16 +7783,16 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -7843,16 +7843,16 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -7868,11 +7868,11 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D346" t="n">
@@ -7908,31 +7908,31 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -7963,16 +7963,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
@@ -7988,11 +7988,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
@@ -8008,11 +8008,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -8043,16 +8043,16 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -8118,17 +8118,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8183,16 +8183,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D362" t="n">
@@ -8228,11 +8228,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="366">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
@@ -8368,11 +8368,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -8408,11 +8408,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="377">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8588,31 +8588,31 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="384">
@@ -8643,16 +8643,16 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="386">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -8783,16 +8783,16 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="392">
@@ -8803,16 +8803,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="394">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396">
@@ -8888,11 +8888,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -8943,16 +8943,16 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="400">
@@ -8963,16 +8963,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="402">
@@ -9008,11 +9008,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="403">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="407">
@@ -9103,16 +9103,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="411">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="412">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="413">
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="414">
@@ -9243,16 +9243,16 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="415">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D415" t="n">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="417">
@@ -9308,11 +9308,11 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="418">
@@ -9328,11 +9328,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="421">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="423">
@@ -9423,16 +9423,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="424">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="425">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="426">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -9503,16 +9503,16 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -9548,11 +9548,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D430" t="n">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432">
@@ -9603,16 +9603,16 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="436">
@@ -9688,11 +9688,11 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="437">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D437" t="n">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="439">
@@ -9748,11 +9748,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="440">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442">
@@ -9803,16 +9803,16 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="443">
@@ -9823,16 +9823,16 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D447" t="n">
@@ -9928,11 +9928,11 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="449">
@@ -9948,11 +9948,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -9968,47 +9968,47 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -10018,17 +10018,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D453" t="n">
@@ -10038,21 +10038,21 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="455">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D457" t="n">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D458" t="n">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="461">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D464" t="n">
@@ -10263,16 +10263,16 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D469" t="n">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="472">
@@ -10408,11 +10408,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="476">
@@ -10483,16 +10483,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="477">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="478">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="479">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="480">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="481">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
@@ -10603,16 +10603,16 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="484">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="485">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="486">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="487">
@@ -10703,12 +10703,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D487" t="n">
@@ -10723,12 +10723,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D488" t="n">
@@ -10743,12 +10743,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D489" t="n">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -10788,11 +10788,11 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -10843,16 +10843,16 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -10863,16 +10863,16 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -10883,16 +10883,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D501" t="n">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="503">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="505">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -11088,111 +11088,111 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="513">
@@ -11223,16 +11223,16 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517">
@@ -11303,12 +11303,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D517" t="n">
@@ -11323,16 +11323,16 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="519">
@@ -11343,16 +11343,16 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="520">
@@ -11363,16 +11363,16 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="521">
@@ -11383,16 +11383,16 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="525">
@@ -11463,12 +11463,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -11483,16 +11483,16 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="530">
@@ -11563,16 +11563,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="531">
@@ -11588,11 +11588,11 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="532">
@@ -11603,16 +11603,16 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="533">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D533" t="n">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="536">
@@ -11683,16 +11683,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="537">
@@ -11703,16 +11703,16 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="538">
@@ -11728,11 +11728,11 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="539">
@@ -11748,11 +11748,11 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -11768,11 +11768,11 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="541">
@@ -11788,11 +11788,11 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="542">
@@ -11803,16 +11803,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="543">
@@ -11823,16 +11823,16 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="545">
@@ -11863,16 +11863,16 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="546">
@@ -11883,16 +11883,16 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="547">
@@ -11903,16 +11903,16 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="548">
@@ -11928,11 +11928,11 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="549">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -11968,11 +11968,11 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="551">
@@ -11983,16 +11983,16 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="552">
@@ -12003,16 +12003,16 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -12032,7 +12032,7 @@
         </is>
       </c>
       <c r="D553" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="554">
@@ -12043,16 +12043,16 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="555">
@@ -12063,16 +12063,16 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="556">
@@ -12083,16 +12083,16 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="557">
@@ -12103,16 +12103,16 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="558">
@@ -12123,16 +12123,16 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D559" t="n">
@@ -12163,16 +12163,16 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="561">
@@ -12183,16 +12183,16 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="562">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -12212,7 +12212,7 @@
         </is>
       </c>
       <c r="D562" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="563">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="D563" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="564">
@@ -12243,16 +12243,16 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D564" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="565">
@@ -12263,16 +12263,16 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D565" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="566">
@@ -12283,16 +12283,16 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567">
@@ -12303,16 +12303,16 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="568">
@@ -12323,16 +12323,16 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="569">
@@ -12343,16 +12343,16 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="570">
@@ -12368,11 +12368,11 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="571">
@@ -12388,11 +12388,11 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="572">
@@ -12403,16 +12403,16 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="573">
@@ -12423,16 +12423,16 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D573" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="574">
@@ -12443,16 +12443,16 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D574" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="575">
@@ -12463,16 +12463,16 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D575" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="576">
@@ -12483,16 +12483,16 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D576" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="577">
@@ -12503,12 +12503,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D577" t="n">
@@ -12523,16 +12523,16 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D578" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="579">
@@ -12543,12 +12543,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D579" t="n">
@@ -12563,12 +12563,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D580" t="n">
@@ -12583,16 +12583,16 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D581" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="582">
@@ -12603,16 +12603,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D582" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="583">
@@ -12623,16 +12623,16 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D583" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="584">
@@ -12648,11 +12648,11 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D584" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="585">
@@ -12668,10 +12668,150 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
+          <t>Faceless</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Hispanic/Latino</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D585" t="n">
+      <c r="D592" t="n">
         <v>13</v>
       </c>
     </row>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -486,37 +486,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3062</v>
+        <v>3020</v>
       </c>
       <c r="C2" t="n">
-        <v>782</v>
+        <v>745</v>
       </c>
       <c r="D2" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="E2" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
         <v>54</v>
       </c>
       <c r="I2" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J2" t="n">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="K2" t="n">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="L2" t="n">
-        <v>5666</v>
+        <v>5525</v>
       </c>
     </row>
     <row r="3">
@@ -526,37 +526,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="C3" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="J3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L3" t="n">
-        <v>678</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4">
@@ -566,37 +566,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>344</v>
+        <v>272</v>
       </c>
       <c r="C4" t="n">
-        <v>205</v>
+        <v>147</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="J4" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="K4" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="L4" t="n">
-        <v>947</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="C5" t="n">
-        <v>348</v>
+        <v>433</v>
       </c>
       <c r="D5" t="n">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
         <v>7</v>
@@ -627,16 +627,16 @@
         <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="J5" t="n">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="K5" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>1422</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="6">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C6" t="n">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="D6" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
         <v>31</v>
@@ -664,19 +664,19 @@
         <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="J6" t="n">
+        <v>120</v>
+      </c>
+      <c r="K6" t="n">
         <v>102</v>
       </c>
-      <c r="K6" t="n">
-        <v>96</v>
-      </c>
       <c r="L6" t="n">
-        <v>1065</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="7">
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C7" t="n">
-        <v>416</v>
+        <v>373</v>
       </c>
       <c r="D7" t="n">
         <v>220</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="J7" t="n">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="K7" t="n">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="L7" t="n">
-        <v>1823</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="8">
@@ -726,37 +726,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J8" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="K8" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L8" t="n">
-        <v>375</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -766,37 +766,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K9" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="L9" t="n">
-        <v>328</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -806,37 +806,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -867,16 +867,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D12" t="n">
         <v>73</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="L12" t="n">
-        <v>1129</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="13">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5348</v>
+        <v>5360</v>
       </c>
       <c r="C13" t="n">
-        <v>2691</v>
+        <v>2699</v>
       </c>
       <c r="D13" t="n">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="E13" t="n">
         <v>303</v>
@@ -944,19 +944,19 @@
         <v>65</v>
       </c>
       <c r="H13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I13" t="n">
-        <v>967</v>
+        <v>988</v>
       </c>
       <c r="J13" t="n">
-        <v>1338</v>
+        <v>1362</v>
       </c>
       <c r="K13" t="n">
-        <v>1132</v>
+        <v>1093</v>
       </c>
       <c r="L13" t="n">
-        <v>13604</v>
+        <v>13638</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D592"/>
+  <dimension ref="A1:D588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1148,11 +1148,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1188,11 +1188,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1268,11 +1268,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1283,16 +1283,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1308,11 +1308,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1328,11 +1328,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1348,11 +1348,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1368,11 +1368,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1388,11 +1388,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1403,16 +1403,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1423,16 +1423,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1468,11 +1468,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1483,16 +1483,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1508,11 +1508,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1528,11 +1528,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1543,16 +1543,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1568,11 +1568,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1628,11 +1628,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1788,31 +1788,31 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ashwagandha</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
@@ -1828,11 +1828,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1848,11 +1848,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
@@ -1868,11 +1868,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -1888,11 +1888,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1908,11 +1908,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
@@ -1928,11 +1928,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
@@ -1948,11 +1948,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
@@ -1983,16 +1983,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>27</v>
+        <v>638</v>
       </c>
     </row>
     <row r="52">
@@ -2008,11 +2008,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>674</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>53</v>
+        <v>298</v>
       </c>
     </row>
     <row r="54">
@@ -2048,11 +2048,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>32</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56">
@@ -2088,11 +2088,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>94</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57">
@@ -2108,11 +2108,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>216</v>
+        <v>443</v>
       </c>
     </row>
     <row r="58">
@@ -2128,11 +2128,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>449</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>353</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>225</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="61">
@@ -2183,16 +2183,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2964</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62">
@@ -2208,11 +2208,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>201</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -2228,11 +2228,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64">
@@ -2248,11 +2248,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2268,11 +2268,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
@@ -2288,11 +2288,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
@@ -2308,11 +2308,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68">
@@ -2328,11 +2328,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69">
@@ -2348,11 +2348,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>123</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
@@ -2368,11 +2368,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>35</v>
+        <v>265</v>
       </c>
     </row>
     <row r="71">
@@ -2383,16 +2383,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>334</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72">
@@ -2408,11 +2408,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2428,11 +2428,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74">
@@ -2448,11 +2448,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2468,11 +2468,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -2488,11 +2488,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -2508,11 +2508,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
@@ -2528,11 +2528,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79">
@@ -2548,11 +2548,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
@@ -2568,11 +2568,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>107</v>
+        <v>361</v>
       </c>
     </row>
     <row r="82">
@@ -2608,11 +2608,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>401</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
@@ -2628,11 +2628,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84">
@@ -2648,11 +2648,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>164</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -2668,11 +2668,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86">
@@ -2688,11 +2688,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87">
@@ -2708,11 +2708,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>38</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88">
@@ -2728,11 +2728,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>202</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90">
@@ -2768,11 +2768,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>128</v>
+        <v>454</v>
       </c>
     </row>
     <row r="91">
@@ -2783,16 +2783,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>453</v>
+        <v>420</v>
       </c>
     </row>
     <row r="92">
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>342</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
@@ -2828,11 +2828,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12</v>
+        <v>149</v>
       </c>
     </row>
     <row r="94">
@@ -2848,11 +2848,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>106</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -2868,11 +2868,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96">
@@ -2888,11 +2888,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97">
@@ -2908,11 +2908,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>27</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98">
@@ -2928,11 +2928,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>132</v>
+        <v>220</v>
       </c>
     </row>
     <row r="99">
@@ -2948,11 +2948,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>159</v>
+        <v>67</v>
       </c>
     </row>
     <row r="100">
@@ -2968,11 +2968,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>61</v>
+        <v>589</v>
       </c>
     </row>
     <row r="101">
@@ -2983,16 +2983,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>444</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
@@ -3008,11 +3008,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -3028,11 +3028,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -3048,11 +3048,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3068,11 +3068,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
@@ -3088,11 +3088,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
@@ -3108,11 +3108,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108">
@@ -3128,11 +3128,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
@@ -3148,11 +3148,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="110">
@@ -3163,16 +3163,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>32</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111">
@@ -3188,11 +3188,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="113">
@@ -3228,11 +3228,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
@@ -3248,11 +3248,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
@@ -3268,11 +3268,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116">
@@ -3288,11 +3288,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117">
@@ -3308,11 +3308,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118">
@@ -3328,11 +3328,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119">
@@ -3348,11 +3348,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>23</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120">
@@ -3363,16 +3363,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>273</v>
+        <v>300</v>
       </c>
     </row>
     <row r="121">
@@ -3388,11 +3388,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>230</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122">
@@ -3408,11 +3408,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
     </row>
     <row r="123">
@@ -3428,11 +3428,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124">
@@ -3448,11 +3448,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="125">
@@ -3468,11 +3468,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="126">
@@ -3488,11 +3488,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>30</v>
+        <v>116</v>
       </c>
     </row>
     <row r="127">
@@ -3508,11 +3508,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>100</v>
+        <v>124</v>
       </c>
     </row>
     <row r="128">
@@ -3528,11 +3528,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>117</v>
+        <v>57</v>
       </c>
     </row>
     <row r="129">
@@ -3548,11 +3548,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>60</v>
+        <v>317</v>
       </c>
     </row>
     <row r="130">
@@ -3563,16 +3563,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>307</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
@@ -3608,11 +3608,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3628,11 +3628,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
@@ -3648,11 +3648,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136">
@@ -3683,16 +3683,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="137">
@@ -3708,11 +3708,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
@@ -3728,11 +3728,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139">
@@ -3748,11 +3748,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141">
@@ -3788,11 +3788,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
@@ -3808,11 +3808,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143">
@@ -3828,11 +3828,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="144">
@@ -3848,11 +3848,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="145">
@@ -3868,31 +3868,31 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>25</v>
+        <v>114</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -3963,16 +3963,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -4008,11 +4008,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -4043,16 +4043,16 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -4063,12 +4063,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -4163,16 +4163,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -4208,11 +4208,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -4223,16 +4223,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -4248,11 +4248,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -4298,21 +4298,21 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -4328,11 +4328,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="169">
@@ -4348,11 +4348,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="170">
@@ -4368,11 +4368,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -4388,11 +4388,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172">
@@ -4408,11 +4408,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="173">
@@ -4428,11 +4428,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>10</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175">
@@ -4463,16 +4463,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="177">
@@ -4508,11 +4508,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -4528,11 +4528,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179">
@@ -4548,11 +4548,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4568,11 +4568,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="182">
@@ -4608,11 +4608,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="184">
@@ -4648,11 +4648,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="185">
@@ -4663,16 +4663,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="186">
@@ -4688,11 +4688,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187">
@@ -4708,11 +4708,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="188">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="191">
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="192">
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="194">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="195">
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="196">
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="200">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="202">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="203">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="205">
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="207">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="208">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="209">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="210">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="211">
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="213">
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="215">
@@ -5268,11 +5268,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="216">
@@ -5288,11 +5288,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217">
@@ -5308,11 +5308,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="218">
@@ -5328,11 +5328,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
     </row>
     <row r="219">
@@ -5348,11 +5348,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="220">
@@ -5368,11 +5368,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>22</v>
+        <v>123</v>
       </c>
     </row>
     <row r="221">
@@ -5383,16 +5383,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>92</v>
+        <v>13</v>
       </c>
     </row>
     <row r="222">
@@ -5408,11 +5408,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228">
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="230">
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232">
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="236">
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237">
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="238">
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="239">
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="241">
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="243">
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="244">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="245">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="246">
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="247">
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="248">
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="249">
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="253">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="254">
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="255">
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="259">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="260">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="261">
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="262">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -6268,11 +6268,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="266">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="267">
@@ -6303,16 +6303,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -6348,11 +6348,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271">
@@ -6388,11 +6388,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276">
@@ -6483,16 +6483,16 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="277">
@@ -6503,16 +6503,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="279">
@@ -6548,11 +6548,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="281">
@@ -6588,11 +6588,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="283">
@@ -6628,11 +6628,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="284">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="285">
@@ -6668,11 +6668,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="286">
@@ -6683,16 +6683,16 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287">
@@ -6708,11 +6708,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -6768,11 +6768,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="292">
@@ -6808,11 +6808,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="293">
@@ -6823,16 +6823,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294">
@@ -6848,11 +6848,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298">
@@ -6923,16 +6923,16 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="299">
@@ -6943,16 +6943,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303">
@@ -7028,11 +7028,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="306">
@@ -7083,16 +7083,16 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -7103,16 +7103,16 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -7123,16 +7123,16 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="310">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="311">
@@ -7183,16 +7183,16 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312">
@@ -7203,16 +7203,16 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -7223,16 +7223,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="315">
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="316">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="317">
@@ -7308,71 +7308,71 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>6</v>
+        <v>268</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>267</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="323">
@@ -7428,11 +7428,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324">
@@ -7448,11 +7448,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>151</v>
       </c>
     </row>
     <row r="325">
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="326">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D326" t="n">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>151</v>
+        <v>34</v>
       </c>
     </row>
     <row r="328">
@@ -7523,16 +7523,16 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
     <row r="329">
@@ -7543,16 +7543,16 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331">
@@ -7588,11 +7588,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
@@ -7608,11 +7608,11 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="334">
@@ -7648,11 +7648,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="337">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D337" t="n">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D338" t="n">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -7803,16 +7803,16 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D344" t="n">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D346" t="n">
@@ -7908,31 +7908,31 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -7963,16 +7963,16 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
@@ -7988,11 +7988,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -8098,17 +8098,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -8118,17 +8118,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D360" t="n">
@@ -8183,16 +8183,16 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D362" t="n">
@@ -8223,16 +8223,16 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -8308,11 +8308,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="370">
@@ -8363,16 +8363,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
@@ -8428,11 +8428,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375">
@@ -8468,11 +8468,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8578,32 +8578,32 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -8623,16 +8623,16 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="384">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D384" t="n">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D386" t="n">
@@ -8708,11 +8708,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="391">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="392">
@@ -8803,16 +8803,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="394">
@@ -8848,11 +8848,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -8888,11 +8888,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="397">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="398">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="399">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -8963,16 +8963,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="402">
@@ -9008,11 +9008,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="403">
@@ -9028,11 +9028,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
@@ -9048,11 +9048,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="405">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407">
@@ -9103,16 +9103,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="411">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="413">
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="417">
@@ -9308,11 +9308,11 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="418">
@@ -9328,11 +9328,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="421">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="423">
@@ -9423,16 +9423,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426">
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="428">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -9548,11 +9548,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -9608,11 +9608,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -9628,11 +9628,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="435">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -9688,11 +9688,11 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="437">
@@ -9708,11 +9708,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="439">
@@ -9748,11 +9748,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="440">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="442">
@@ -9808,11 +9808,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="443">
@@ -9828,11 +9828,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="445">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="446">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="448">
@@ -9928,11 +9928,11 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -9948,11 +9948,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="450">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -9988,47 +9988,47 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D453" t="n">
@@ -10038,21 +10038,21 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="457">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D457" t="n">
@@ -10123,16 +10123,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10172,7 +10172,7 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="462">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D463" t="n">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D464" t="n">
@@ -10263,16 +10263,16 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="468">
@@ -10323,16 +10323,16 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="469">
@@ -10343,12 +10343,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D469" t="n">
@@ -10363,16 +10363,16 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="471">
@@ -10383,16 +10383,16 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472">
@@ -10408,11 +10408,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="476">
@@ -10483,16 +10483,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="483">
@@ -10628,11 +10628,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="484">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="485">
@@ -10663,16 +10663,16 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486">
@@ -10688,11 +10688,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487">
@@ -10708,11 +10708,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -10728,11 +10728,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="490">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="491">
@@ -10788,11 +10788,11 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D493" t="n">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="495">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="496">
@@ -10888,11 +10888,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499">
@@ -10948,11 +10948,11 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -10968,11 +10968,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="503">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="506">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D506" t="n">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="508">
@@ -11128,71 +11128,71 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Turmeric Curcumin</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="513">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="518">
@@ -11328,11 +11328,11 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>29</v>
+        <v>112</v>
       </c>
     </row>
     <row r="520">
@@ -11363,16 +11363,16 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="521">
@@ -11383,16 +11383,16 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>116</v>
+        <v>5</v>
       </c>
     </row>
     <row r="523">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D523" t="n">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="525">
@@ -11468,11 +11468,11 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="526">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="527">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530">
@@ -11563,16 +11563,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="531">
@@ -11588,11 +11588,11 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="532">
@@ -11608,11 +11608,11 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="533">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="534">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536">
@@ -11683,16 +11683,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="537">
@@ -11703,16 +11703,16 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -11728,11 +11728,11 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
     </row>
     <row r="539">
@@ -11748,11 +11748,11 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="540">
@@ -11768,11 +11768,11 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="541">
@@ -11788,11 +11788,11 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="542">
@@ -11808,11 +11808,11 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="543">
@@ -11828,11 +11828,11 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="545">
@@ -11863,16 +11863,16 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546">
@@ -11883,16 +11883,16 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="547">
@@ -11903,16 +11903,16 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="548">
@@ -11928,11 +11928,11 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="549">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="550">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D550" t="n">
@@ -11988,11 +11988,11 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="552">
@@ -12008,11 +12008,11 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="553">
@@ -12023,16 +12023,16 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="554">
@@ -12043,16 +12043,16 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555">
@@ -12063,16 +12063,16 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556">
@@ -12083,16 +12083,16 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="557">
@@ -12108,11 +12108,11 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="558">
@@ -12128,11 +12128,11 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="559">
@@ -12148,11 +12148,11 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="560">
@@ -12163,16 +12163,16 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="561">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D561" t="n">
@@ -12203,16 +12203,16 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563">
@@ -12228,11 +12228,11 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564">
@@ -12248,11 +12248,11 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D564" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="565">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D565" t="n">
@@ -12288,11 +12288,11 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="567">
@@ -12303,16 +12303,16 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="568">
@@ -12323,16 +12323,16 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="569">
@@ -12343,16 +12343,16 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="570">
@@ -12368,11 +12368,11 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="571">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D571" t="n">
@@ -12408,11 +12408,11 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="573">
@@ -12428,11 +12428,11 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D573" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="574">
@@ -12448,11 +12448,11 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D574" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="575">
@@ -12468,11 +12468,11 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D575" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="576">
@@ -12483,16 +12483,16 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D576" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="577">
@@ -12503,16 +12503,16 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D577" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="578">
@@ -12523,16 +12523,16 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D578" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="579">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D579" t="n">
@@ -12568,11 +12568,11 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D580" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="581">
@@ -12583,16 +12583,16 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D581" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="582">
@@ -12603,16 +12603,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D582" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="583">
@@ -12623,16 +12623,16 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D583" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="584">
@@ -12648,11 +12648,11 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D584" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="585">
@@ -12668,11 +12668,11 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D585" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="586">
@@ -12688,11 +12688,11 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D586" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="587">
@@ -12708,11 +12708,11 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D587" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="588">
@@ -12728,91 +12728,11 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D588" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="D589" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>South Asian</t>
-        </is>
-      </c>
-      <c r="D590" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D591" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>Turmeric Curcumin</t>
-        </is>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>White/European</t>
-        </is>
-      </c>
-      <c r="D592" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -633,10 +633,10 @@
         <v>179</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="n">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="6">
@@ -673,10 +673,10 @@
         <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L6" t="n">
-        <v>1183</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         <v>183</v>
       </c>
       <c r="K7" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L7" t="n">
-        <v>1735</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="8">
@@ -793,10 +793,10 @@
         <v>28</v>
       </c>
       <c r="K9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="n">
         <v>367</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="L12" t="n">
-        <v>1138</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="13">
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5360</v>
+        <v>5361</v>
       </c>
       <c r="C13" t="n">
         <v>2699</v>
@@ -953,10 +953,10 @@
         <v>1362</v>
       </c>
       <c r="K13" t="n">
-        <v>1093</v>
+        <v>1109</v>
       </c>
       <c r="L13" t="n">
-        <v>13638</v>
+        <v>13655</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D588"/>
+  <dimension ref="A1:D592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="175">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="186">
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="187">
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="192">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="194">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="202">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="210">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="211">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="212">
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="213">
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="215">
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="218">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="219">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="221">
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="238">
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="246">
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="262">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275">
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="277">
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="279">
@@ -6552,7 +6552,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="282">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="283">
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="284">
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="286">
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="287">
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288">
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291">
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="292">
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="293">
@@ -6923,16 +6923,16 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -6968,11 +6968,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="301">
@@ -6988,11 +6988,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D303" t="n">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306">
@@ -7083,16 +7083,16 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="307">
@@ -7103,16 +7103,16 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="308">
@@ -7123,16 +7123,16 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="309">
@@ -7148,11 +7148,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
@@ -7163,16 +7163,16 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -7183,16 +7183,16 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -7203,16 +7203,16 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -7228,11 +7228,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="314">
@@ -7248,11 +7248,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315">
@@ -7268,11 +7268,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -7308,71 +7308,71 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>268</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="321">
@@ -7388,11 +7388,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>268</v>
       </c>
     </row>
     <row r="322">
@@ -7408,11 +7408,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323">
@@ -7428,11 +7428,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="324">
@@ -7448,11 +7448,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="326">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D326" t="n">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>34</v>
+        <v>151</v>
       </c>
     </row>
     <row r="328">
@@ -7523,16 +7523,16 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="329">
@@ -7543,16 +7543,16 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="330">
@@ -7563,16 +7563,16 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="331">
@@ -7588,11 +7588,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="332">
@@ -7608,11 +7608,11 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -7628,11 +7628,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="334">
@@ -7648,11 +7648,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="337">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D337" t="n">
@@ -7723,16 +7723,16 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="340">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -7783,16 +7783,16 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D344" t="n">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D345" t="n">
@@ -7883,16 +7883,16 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347">
@@ -7903,27 +7903,27 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -7938,17 +7938,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -7958,17 +7958,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -8028,11 +8028,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -8048,11 +8048,11 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -8083,52 +8083,52 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -8138,17 +8138,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D360" t="n">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -8288,11 +8288,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="367">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -8328,11 +8328,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
@@ -8348,11 +8348,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="370">
@@ -8363,16 +8363,16 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -8383,16 +8383,16 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="372">
@@ -8403,16 +8403,16 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="373">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="375">
@@ -8463,16 +8463,16 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -8512,7 +8512,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="378">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8578,37 +8578,37 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D382" t="n">
@@ -8618,21 +8618,21 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -8643,16 +8643,16 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="385">
@@ -8663,16 +8663,16 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
@@ -8688,11 +8688,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="387">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -8748,11 +8748,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390">
@@ -8768,11 +8768,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="392">
@@ -8803,16 +8803,16 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="393">
@@ -8823,16 +8823,16 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="394">
@@ -8843,16 +8843,16 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="395">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="396">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
@@ -8928,11 +8928,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -8963,16 +8963,16 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="402">
@@ -9008,11 +9008,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="403">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -9048,11 +9048,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -9083,16 +9083,16 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -9103,16 +9103,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="408">
@@ -9128,11 +9128,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="409">
@@ -9148,11 +9148,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -9168,11 +9168,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="411">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="414">
@@ -9248,11 +9248,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="418">
@@ -9328,11 +9328,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="419">
@@ -9348,11 +9348,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="420">
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="421">
@@ -9388,11 +9388,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="422">
@@ -9408,11 +9408,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="423">
@@ -9423,16 +9423,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="425">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="426">
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="427">
@@ -9508,11 +9508,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -9523,16 +9523,16 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D430" t="n">
@@ -9588,11 +9588,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D432" t="n">
@@ -9628,11 +9628,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="437">
@@ -9708,11 +9708,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="438">
@@ -9728,11 +9728,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -9748,11 +9748,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="440">
@@ -9768,11 +9768,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="441">
@@ -9788,11 +9788,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="442">
@@ -9808,11 +9808,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="443">
@@ -9828,11 +9828,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="447">
@@ -9903,16 +9903,16 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -9923,16 +9923,16 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -9948,11 +9948,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="450">
@@ -9968,11 +9968,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="451">
@@ -9988,71 +9988,71 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="455">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -10103,16 +10103,16 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -10123,16 +10123,16 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -10143,16 +10143,16 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="460">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D460" t="n">
@@ -10183,16 +10183,16 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
@@ -10203,16 +10203,16 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D463" t="n">
@@ -10248,11 +10248,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="465">
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -10288,11 +10288,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467">
@@ -10303,16 +10303,16 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -10343,16 +10343,16 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="470">
@@ -10368,11 +10368,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="471">
@@ -10388,11 +10388,11 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="472">
@@ -10408,11 +10408,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473">
@@ -10428,11 +10428,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -10448,11 +10448,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="475">
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="476">
@@ -10483,16 +10483,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="477">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="479">
@@ -10548,11 +10548,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -10588,11 +10588,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482">
@@ -10608,11 +10608,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
@@ -10628,11 +10628,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="484">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="485">
@@ -10663,16 +10663,16 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D485" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="486">
@@ -10683,16 +10683,16 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="487">
@@ -10708,11 +10708,11 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="488">
@@ -10728,11 +10728,11 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -10763,16 +10763,16 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -10783,16 +10783,16 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D491" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="492">
@@ -10808,11 +10808,11 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="493">
@@ -10828,11 +10828,11 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="494">
@@ -10848,11 +10848,11 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -10868,11 +10868,11 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -10888,11 +10888,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="500">
@@ -10968,11 +10968,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -10983,16 +10983,16 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
@@ -11003,16 +11003,16 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="503">
@@ -11023,16 +11023,16 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -11048,11 +11048,11 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="505">
@@ -11068,11 +11068,11 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="506">
@@ -11088,11 +11088,11 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507">
@@ -11108,11 +11108,11 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="508">
@@ -11128,71 +11128,71 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="512">
@@ -11203,16 +11203,16 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="513">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -11248,11 +11248,11 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="515">
@@ -11268,11 +11268,11 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="516">
@@ -11288,11 +11288,11 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517">
@@ -11308,11 +11308,11 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="518">
@@ -11328,11 +11328,11 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="519">
@@ -11348,11 +11348,11 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>112</v>
+        <v>29</v>
       </c>
     </row>
     <row r="520">
@@ -11363,16 +11363,16 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="521">
@@ -11383,16 +11383,16 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -11403,16 +11403,16 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="523">
@@ -11428,11 +11428,11 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="524">
@@ -11448,11 +11448,11 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="525">
@@ -11468,11 +11468,11 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="526">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="527">
@@ -11503,16 +11503,16 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="528">
@@ -11523,16 +11523,16 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="530">
@@ -11568,11 +11568,11 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="531">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D531" t="n">
@@ -11608,11 +11608,11 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="533">
@@ -11628,11 +11628,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="534">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="536">
@@ -11683,16 +11683,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="537">
@@ -11708,11 +11708,11 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="538">
@@ -11728,11 +11728,11 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539">
@@ -11748,11 +11748,11 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="540">
@@ -11768,11 +11768,11 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -11788,11 +11788,11 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="542">
@@ -11808,11 +11808,11 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="543">
@@ -11828,11 +11828,11 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="545">
@@ -11863,16 +11863,16 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="546">
@@ -11883,16 +11883,16 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="547">
@@ -11908,11 +11908,11 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="548">
@@ -11928,11 +11928,11 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="550">
@@ -11968,11 +11968,11 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="551">
@@ -11988,11 +11988,11 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552">
@@ -12008,11 +12008,11 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="553">
@@ -12023,16 +12023,16 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="554">
@@ -12043,16 +12043,16 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="555">
@@ -12063,16 +12063,16 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="556">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D556" t="n">
@@ -12108,11 +12108,11 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="558">
@@ -12128,11 +12128,11 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559">
@@ -12148,11 +12148,11 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="560">
@@ -12163,16 +12163,16 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="561">
@@ -12183,16 +12183,16 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="562">
@@ -12203,16 +12203,16 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="563">
@@ -12228,11 +12228,11 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="564">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D564" t="n">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D565" t="n">
@@ -12288,11 +12288,11 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567">
@@ -12303,16 +12303,16 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="568">
@@ -12323,16 +12323,16 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="569">
@@ -12343,16 +12343,16 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570">
@@ -12363,16 +12363,16 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="571">
@@ -12388,11 +12388,11 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="572">
@@ -12408,11 +12408,11 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="573">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D573" t="n">
@@ -12448,11 +12448,11 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D574" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="575">
@@ -12468,11 +12468,11 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D575" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="576">
@@ -12483,16 +12483,16 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D576" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="577">
@@ -12503,16 +12503,16 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D577" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="578">
@@ -12523,16 +12523,16 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D578" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="579">
@@ -12543,16 +12543,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D579" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="580">
@@ -12568,11 +12568,11 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D580" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="581">
@@ -12583,16 +12583,16 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D581" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="582">
@@ -12603,16 +12603,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D582" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="583">
@@ -12623,16 +12623,16 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D583" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="584">
@@ -12643,16 +12643,16 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D584" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="585">
@@ -12668,11 +12668,11 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D585" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="586">
@@ -12688,11 +12688,11 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D586" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="587">
@@ -12708,11 +12708,11 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D587" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="588">
@@ -12728,11 +12728,91 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="D588" t="n">
-        <v>20</v>
+      <c r="D592" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/slab_ethnicity_matrix.xlsx
+++ b/slab_ethnicity_matrix.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3020</v>
+        <v>3021</v>
       </c>
       <c r="C2" t="n">
         <v>745</v>
@@ -516,7 +516,7 @@
         <v>235</v>
       </c>
       <c r="L2" t="n">
-        <v>5525</v>
+        <v>5526</v>
       </c>
     </row>
     <row r="3">
@@ -633,10 +633,10 @@
         <v>179</v>
       </c>
       <c r="K5" t="n">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="L5" t="n">
-        <v>1846</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="6">
@@ -673,10 +673,10 @@
         <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L6" t="n">
-        <v>1187</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         <v>183</v>
       </c>
       <c r="K7" t="n">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="L7" t="n">
-        <v>1737</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
         <v>103</v>
@@ -753,10 +753,10 @@
         <v>48</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="L8" t="n">
-        <v>427</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -793,10 +793,10 @@
         <v>28</v>
       </c>
       <c r="K9" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L9" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -833,10 +833,10 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L10" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -873,10 +873,10 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -889,7 +889,7 @@
         <v>71</v>
       </c>
       <c r="C12" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D12" t="n">
         <v>73</v>
@@ -913,10 +913,10 @@
         <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>297</v>
+        <v>338</v>
       </c>
       <c r="L12" t="n">
-        <v>1147</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="13">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5361</v>
+        <v>5363</v>
       </c>
       <c r="C13" t="n">
-        <v>2699</v>
+        <v>2702</v>
       </c>
       <c r="D13" t="n">
         <v>1225</v>
@@ -953,10 +953,10 @@
         <v>1362</v>
       </c>
       <c r="K13" t="n">
-        <v>1109</v>
+        <v>1265</v>
       </c>
       <c r="L13" t="n">
-        <v>13655</v>
+        <v>13816</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D592"/>
+  <dimension ref="A1:D610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="52">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="82">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="90">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="129">
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="169">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="175">
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="186">
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="187">
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="194">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="203">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="207">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="209">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="210">
@@ -5172,7 +5172,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="211">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="212">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216">
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="218">
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="220">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="221">
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="239">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="241">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="246">
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="247">
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="248">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="254">
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="267">
@@ -6308,11 +6308,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -6328,11 +6328,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -6363,16 +6363,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -6388,11 +6388,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="272">
@@ -6408,11 +6408,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="275">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -6483,16 +6483,16 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277">
@@ -6508,11 +6508,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="278">
@@ -6528,11 +6528,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -6548,11 +6548,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="280">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -6588,11 +6588,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="282">
@@ -6608,11 +6608,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283">
@@ -6628,11 +6628,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="284">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="285">
@@ -6668,11 +6668,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="286">
@@ -6683,16 +6683,16 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="287">
@@ -6708,11 +6708,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="288">
@@ -6728,11 +6728,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289">
@@ -6748,11 +6748,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290">
@@ -6768,11 +6768,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -6788,11 +6788,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292">
@@ -6808,11 +6808,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="293">
@@ -6823,16 +6823,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="294">
@@ -6843,16 +6843,16 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="295">
@@ -6868,11 +6868,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="296">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -6908,11 +6908,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300">
@@ -6963,16 +6963,16 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
@@ -6983,16 +6983,16 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -7003,16 +7003,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -7028,11 +7028,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="304">
@@ -7048,11 +7048,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="305">
@@ -7068,11 +7068,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -7128,11 +7128,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309">
@@ -7143,16 +7143,16 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310">
@@ -7163,16 +7163,16 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="311">
@@ -7183,16 +7183,16 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="312">
@@ -7208,11 +7208,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -7223,16 +7223,16 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -7243,16 +7243,16 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -7263,16 +7263,16 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -7288,11 +7288,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="317">
@@ -7308,11 +7308,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318">
@@ -7328,11 +7328,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
@@ -7368,71 +7368,71 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>268</v>
+        <v>6</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="324">
@@ -7448,11 +7448,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>1</v>
+        <v>268</v>
       </c>
     </row>
     <row r="325">
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326">
@@ -7488,11 +7488,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="327">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -7528,11 +7528,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="329">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D329" t="n">
@@ -7568,11 +7568,11 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>34</v>
+        <v>151</v>
       </c>
     </row>
     <row r="331">
@@ -7583,16 +7583,16 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="332">
@@ -7603,16 +7603,16 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="333">
@@ -7623,16 +7623,16 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="334">
@@ -7648,11 +7648,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="335">
@@ -7668,11 +7668,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -7688,11 +7688,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="337">
@@ -7708,11 +7708,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339">
@@ -7748,11 +7748,11 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="340">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -7783,16 +7783,16 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -7803,16 +7803,16 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="343">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -7843,16 +7843,16 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D345" t="n">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D347" t="n">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -7943,16 +7943,16 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="350">
@@ -7963,27 +7963,27 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -7998,17 +7998,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -8018,21 +8018,21 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354">
@@ -8043,12 +8043,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -8088,11 +8088,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -8108,11 +8108,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -8123,12 +8123,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -8143,52 +8143,52 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -8198,17 +8198,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D362" t="n">
@@ -8218,17 +8218,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D363" t="n">
@@ -8243,16 +8243,16 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="365">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8283,16 +8283,16 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
@@ -8303,16 +8303,16 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -8343,16 +8343,16 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="372">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="373">
@@ -8423,16 +8423,16 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="374">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -8483,16 +8483,16 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="377">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -8523,16 +8523,16 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="379">
@@ -8543,16 +8543,16 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="380">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -8583,16 +8583,16 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="383">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -8632,83 +8632,83 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -8718,57 +8718,57 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -8778,17 +8778,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -8798,17 +8798,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D392" t="n">
@@ -8818,117 +8818,117 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -8938,41 +8938,41 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="401">
@@ -8983,16 +8983,16 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="402">
@@ -9003,16 +9003,16 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
@@ -9023,16 +9023,16 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="404">
@@ -9043,16 +9043,16 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405">
@@ -9063,16 +9063,16 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="406">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D406" t="n">
@@ -9103,16 +9103,16 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
@@ -9123,16 +9123,16 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -9163,16 +9163,16 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="411">
@@ -9183,16 +9183,16 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="412">
@@ -9203,16 +9203,16 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="413">
@@ -9223,16 +9223,16 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="414">
@@ -9243,16 +9243,16 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -9263,16 +9263,16 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -9283,16 +9283,16 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="417">
@@ -9303,16 +9303,16 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
     </row>
     <row r="418">
@@ -9323,16 +9323,16 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="419">
@@ -9343,16 +9343,16 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="420">
@@ -9363,16 +9363,16 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -9383,16 +9383,16 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -9403,16 +9403,16 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -9423,16 +9423,16 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424">
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="425">
@@ -9463,16 +9463,16 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="426">
@@ -9483,16 +9483,16 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
@@ -9503,16 +9503,16 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="428">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="430">
@@ -9563,16 +9563,16 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="431">
@@ -9583,16 +9583,16 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="432">
@@ -9603,16 +9603,16 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="433">
@@ -9623,16 +9623,16 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="434">
@@ -9643,16 +9643,16 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="435">
@@ -9663,16 +9663,16 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="436">
@@ -9683,16 +9683,16 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="437">
@@ -9703,16 +9703,16 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="438">
@@ -9723,16 +9723,16 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="439">
@@ -9743,16 +9743,16 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="440">
@@ -9763,16 +9763,16 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="441">
@@ -9783,16 +9783,16 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="442">
@@ -9803,16 +9803,16 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="443">
@@ -9823,16 +9823,16 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="444">
@@ -9843,16 +9843,16 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
@@ -9863,16 +9863,16 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
@@ -9883,16 +9883,16 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D447" t="n">
@@ -9923,12 +9923,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D448" t="n">
@@ -9943,16 +9943,16 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -9983,12 +9983,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D451" t="n">
@@ -10003,16 +10003,16 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -10023,16 +10023,16 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="454">
@@ -10043,47 +10043,47 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10092,23 +10092,23 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D457" t="n">
@@ -10118,112 +10118,112 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -10232,18 +10232,18 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10252,23 +10252,23 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -10278,77 +10278,77 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D469" t="n">
@@ -10358,41 +10358,41 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="472">
@@ -10403,16 +10403,16 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -10423,16 +10423,16 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -10443,16 +10443,16 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -10463,16 +10463,16 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -10483,16 +10483,16 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="477">
@@ -10503,16 +10503,16 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -10523,16 +10523,16 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -10543,16 +10543,16 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -10563,16 +10563,16 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -10583,16 +10583,16 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="482">
@@ -10603,16 +10603,16 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483">
@@ -10623,16 +10623,16 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
@@ -10643,16 +10643,16 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="486">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="487">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -10712,7 +10712,7 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="488">
@@ -10723,16 +10723,16 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="489">
@@ -10743,16 +10743,16 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D491" t="n">
@@ -10803,16 +10803,16 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="493">
@@ -10823,16 +10823,16 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="494">
@@ -10843,16 +10843,16 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="495">
@@ -10863,16 +10863,16 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="496">
@@ -10883,16 +10883,16 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -10903,16 +10903,16 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -10923,16 +10923,16 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499">
@@ -10943,16 +10943,16 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="502">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="D502" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="504">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="505">
@@ -11063,16 +11063,16 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -11083,12 +11083,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D506" t="n">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D507" t="n">
@@ -11123,16 +11123,16 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="509">
@@ -11143,16 +11143,16 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="510">
@@ -11163,16 +11163,16 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="511">
@@ -11183,52 +11183,52 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -11238,301 +11238,301 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>115</v>
+        <v>7</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="529">
@@ -11543,16 +11543,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530">
@@ -11563,16 +11563,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D530" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="531">
@@ -11583,16 +11583,16 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532">
@@ -11603,16 +11603,16 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="533">
@@ -11623,16 +11623,16 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="534">
@@ -11643,16 +11643,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D534" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535">
@@ -11663,16 +11663,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="536">
@@ -11683,16 +11683,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="537">
@@ -11703,16 +11703,16 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="538">
@@ -11723,16 +11723,16 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="539">
@@ -11743,16 +11743,16 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="540">
@@ -11763,16 +11763,16 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D540" t="n">
-        <v>2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="541">
@@ -11783,16 +11783,16 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="542">
@@ -11803,16 +11803,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
@@ -11823,16 +11823,16 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="544">
@@ -11843,16 +11843,16 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="545">
@@ -11863,16 +11863,16 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="546">
@@ -11883,16 +11883,16 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="547">
@@ -11903,16 +11903,16 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="548">
@@ -11923,16 +11923,16 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="549">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="D549" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="550">
@@ -11963,16 +11963,16 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -11983,16 +11983,16 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D551" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="552">
@@ -12003,16 +12003,16 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="553">
@@ -12023,16 +12023,16 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="554">
@@ -12043,16 +12043,16 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="555">
@@ -12063,16 +12063,16 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="556">
@@ -12083,16 +12083,16 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="D557" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="558">
@@ -12123,16 +12123,16 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -12143,16 +12143,16 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="560">
@@ -12163,16 +12163,16 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="561">
@@ -12183,16 +12183,16 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D561" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="562">
@@ -12203,16 +12203,16 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
     </row>
     <row r="563">
@@ -12223,16 +12223,16 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="564">
@@ -12243,16 +12243,16 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D564" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="565">
@@ -12263,16 +12263,16 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Hispanic/Latino</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D565" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="566">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D566" t="n">
@@ -12303,16 +12303,16 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="568">
@@ -12323,16 +12323,16 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="569">
@@ -12343,16 +12343,16 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="570">
@@ -12363,16 +12363,16 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="571">
@@ -12383,16 +12383,16 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="572">
@@ -12403,16 +12403,16 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>East/SE Asian</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D572" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="573">
@@ -12423,16 +12423,16 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D573" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="574">
@@ -12443,16 +12443,16 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D574" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -12463,16 +12463,16 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D575" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576">
@@ -12483,16 +12483,16 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Middle Eastern/Arab</t>
         </is>
       </c>
       <c r="D576" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="577">
@@ -12503,16 +12503,16 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D577" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
@@ -12523,16 +12523,16 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D578" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="579">
@@ -12543,16 +12543,16 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D579" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="580">
@@ -12563,16 +12563,16 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D580" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="581">
@@ -12583,16 +12583,16 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D581" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="582">
@@ -12603,16 +12603,16 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D582" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="583">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hispanic/Latino</t>
         </is>
       </c>
       <c r="D583" t="n">
@@ -12643,16 +12643,16 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>White/European</t>
+          <t>Mixed/Ambiguous</t>
         </is>
       </c>
       <c r="D584" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585">
@@ -12663,16 +12663,16 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Black/African</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="D585" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="586">
@@ -12683,16 +12683,16 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Faceless</t>
+          <t>South Asian</t>
         </is>
       </c>
       <c r="D586" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="587">
@@ -12703,16 +12703,16 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Middle Eastern/Arab</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D587" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="588">
@@ -12723,16 +12723,16 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Mixed/Ambiguous</t>
+          <t>White/European</t>
         </is>
       </c>
       <c r="D588" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="589">
@@ -12743,16 +12743,16 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Black/African</t>
         </is>
       </c>
       <c r="D589" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="590">
@@ -12763,16 +12763,16 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>South Asian</t>
+          <t>East/SE Asian</t>
         </is>
       </c>
       <c r="D590" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="591">
@@ -12783,16 +12783,16 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Faceless</t>
         </is>
       </c>
       <c r="D591" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="592">
@@ -12803,15 +12803,375 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Middle Eastern/Arab</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>South Asian</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <